--- a/output/Data and Chart Outputs/puertorico_generation_monthly.xlsx
+++ b/output/Data and Chart Outputs/puertorico_generation_monthly.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By sector" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By fuel type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="By sector" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="By fuel type" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="164" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,10 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -142,13 +143,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -158,6 +159,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -172,10 +174,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -200,10 +202,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -228,10 +230,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -256,10 +258,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -284,10 +286,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -312,10 +314,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -340,10 +342,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -368,10 +370,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -398,11 +400,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="10"/>
@@ -419,8 +433,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -430,13 +444,14 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -444,12 +459,13 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -458,7 +474,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -473,9 +489,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -907,7 +923,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B2" t="n">
@@ -936,7 +952,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B3" t="n">
@@ -965,7 +981,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>42430</v>
       </c>
       <c r="B4" t="n">
@@ -994,7 +1010,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B5" t="n">
@@ -1023,7 +1039,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>42491</v>
       </c>
       <c r="B6" t="n">
@@ -1052,7 +1068,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>42522</v>
       </c>
       <c r="B7" t="n">
@@ -1081,7 +1097,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B8" t="n">
@@ -1110,7 +1126,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B9" t="n">
@@ -1139,7 +1155,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>42614</v>
       </c>
       <c r="B10" t="n">
@@ -1168,7 +1184,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B11" t="n">
@@ -1197,7 +1213,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>42675</v>
       </c>
       <c r="B12" t="n">
@@ -1226,7 +1242,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>42705</v>
       </c>
       <c r="B13" t="n">
@@ -1255,7 +1271,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B14" t="n">
@@ -1284,7 +1300,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>42767</v>
       </c>
       <c r="B15" t="n">
@@ -1313,7 +1329,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>42795</v>
       </c>
       <c r="B16" t="n">
@@ -1342,7 +1358,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B17" t="n">
@@ -1371,7 +1387,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B18" t="n">
@@ -1400,7 +1416,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>42887</v>
       </c>
       <c r="B19" t="n">
@@ -1429,7 +1445,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B20" t="n">
@@ -1458,7 +1474,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>42948</v>
       </c>
       <c r="B21" t="n">
@@ -1487,7 +1503,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>42979</v>
       </c>
       <c r="B22" t="n">
@@ -1516,7 +1532,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B23" t="n">
@@ -1545,7 +1561,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>43040</v>
       </c>
       <c r="B24" t="n">
@@ -1574,7 +1590,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>43070</v>
       </c>
       <c r="B25" t="n">
@@ -1603,7 +1619,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B26" t="n">
@@ -1632,7 +1648,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>43132</v>
       </c>
       <c r="B27" t="n">
@@ -1661,7 +1677,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>43160</v>
       </c>
       <c r="B28" t="n">
@@ -1690,7 +1706,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B29" t="n">
@@ -1719,7 +1735,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>43221</v>
       </c>
       <c r="B30" t="n">
@@ -1748,7 +1764,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>43252</v>
       </c>
       <c r="B31" t="n">
@@ -1777,7 +1793,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B32" t="n">
@@ -1806,7 +1822,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>43313</v>
       </c>
       <c r="B33" t="n">
@@ -1835,7 +1851,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>43344</v>
       </c>
       <c r="B34" t="n">
@@ -1864,7 +1880,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B35" t="n">
@@ -1893,7 +1909,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>43405</v>
       </c>
       <c r="B36" t="n">
@@ -1922,7 +1938,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>43435</v>
       </c>
       <c r="B37" t="n">
@@ -1951,7 +1967,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B38" t="n">
@@ -1980,7 +1996,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>43497</v>
       </c>
       <c r="B39" t="n">
@@ -2009,7 +2025,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>43525</v>
       </c>
       <c r="B40" t="n">
@@ -2038,7 +2054,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B41" t="n">
@@ -2067,7 +2083,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>43586</v>
       </c>
       <c r="B42" t="n">
@@ -2096,7 +2112,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>43617</v>
       </c>
       <c r="B43" t="n">
@@ -2125,7 +2141,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B44" t="n">
@@ -2154,7 +2170,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="B45" t="n">
@@ -2183,7 +2199,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>43709</v>
       </c>
       <c r="B46" t="n">
@@ -2212,7 +2228,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B47" t="n">
@@ -2241,7 +2257,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>43770</v>
       </c>
       <c r="B48" t="n">
@@ -2270,7 +2286,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>43800</v>
       </c>
       <c r="B49" t="n">
@@ -2299,7 +2315,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B50" t="n">
@@ -2328,7 +2344,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>43862</v>
       </c>
       <c r="B51" t="n">
@@ -2357,7 +2373,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>43891</v>
       </c>
       <c r="B52" t="n">
@@ -2386,7 +2402,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B53" t="n">
@@ -2415,7 +2431,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>43952</v>
       </c>
       <c r="B54" t="n">
@@ -2444,7 +2460,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B55" t="n">
@@ -2473,7 +2489,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B56" t="n">
@@ -2502,7 +2518,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>44044</v>
       </c>
       <c r="B57" t="n">
@@ -2531,7 +2547,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>44075</v>
       </c>
       <c r="B58" t="n">
@@ -2560,7 +2576,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B59" t="n">
@@ -2589,7 +2605,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>44136</v>
       </c>
       <c r="B60" t="n">
@@ -2618,7 +2634,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>44166</v>
       </c>
       <c r="B61" t="n">
@@ -2647,7 +2663,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B62" t="n">
@@ -2676,7 +2692,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B63" t="n">
@@ -2705,7 +2721,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B64" t="n">
@@ -2734,7 +2750,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B65" t="n">
@@ -2763,7 +2779,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B66" t="n">
@@ -2792,7 +2808,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B67" t="n">
@@ -2821,7 +2837,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B68" t="n">
@@ -2850,7 +2866,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B69" t="n">
@@ -2879,7 +2895,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B70" t="n">
@@ -2908,7 +2924,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B71" t="n">
@@ -2937,7 +2953,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B72" t="n">
@@ -2966,7 +2982,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B73" t="n">
@@ -2995,7 +3011,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B74" t="n">
@@ -3024,7 +3040,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B75" t="n">
@@ -3053,7 +3069,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B76" t="n">
@@ -3082,7 +3098,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B77" t="n">
@@ -3111,7 +3127,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B78" t="n">
@@ -3140,7 +3156,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B79" t="n">
@@ -3169,7 +3185,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B80" t="n">
@@ -3198,7 +3214,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B81" t="n">
@@ -3227,7 +3243,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B82" t="n">
@@ -3256,7 +3272,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B83" t="n">
@@ -3285,7 +3301,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B84" t="n">
@@ -3314,7 +3330,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B85" t="n">
@@ -3343,7 +3359,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B86" t="n">
@@ -3372,7 +3388,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B87" t="n">
@@ -3401,7 +3417,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B88" t="n">
@@ -3430,7 +3446,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B89" t="n">
@@ -3459,7 +3475,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B90" t="n">
@@ -3488,7 +3504,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B91" t="n">
@@ -3517,7 +3533,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B92" t="n">
@@ -3546,7 +3562,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B93" t="n">
@@ -3575,7 +3591,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B94" t="n">
@@ -3604,7 +3620,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B95" t="n">
@@ -3633,7 +3649,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B96" t="n">
@@ -3662,7 +3678,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B97" t="n">
@@ -3691,7 +3707,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B98" t="n">
@@ -3720,7 +3736,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B99" t="n">
@@ -3749,7 +3765,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B100" t="n">
@@ -3778,7 +3794,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B101" t="n">
@@ -3807,7 +3823,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B102" t="n">
@@ -3836,7 +3852,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B103" t="n">
@@ -3865,7 +3881,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B104" t="n">
@@ -3894,7 +3910,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B105" t="n">
@@ -3923,7 +3939,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B106" t="n">
@@ -3952,7 +3968,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B107" t="n">
@@ -3981,7 +3997,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B108" t="n">
@@ -4010,7 +4026,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B109" t="n">
@@ -4039,7 +4055,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B110" t="n">
@@ -4068,7 +4084,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B111" t="n">
@@ -4097,7 +4113,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B112" t="n">
@@ -4126,7 +4142,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B113" t="n">
@@ -4155,7 +4171,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B114" t="n">
@@ -4184,7 +4200,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B115" t="n">
@@ -4213,7 +4229,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B116" t="n">
@@ -4242,7 +4258,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B117" t="n">
@@ -4271,7 +4287,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B118" t="n">
@@ -4300,7 +4316,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B119" t="n">
@@ -4329,7 +4345,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B120" t="n">
@@ -4358,7 +4374,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B121" t="n">
@@ -4387,7 +4403,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B122" t="n">
@@ -4416,7 +4432,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B123" t="n">
@@ -4445,7 +4461,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B124" t="n">
@@ -4474,7 +4490,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B125" t="n">
@@ -4503,7 +4519,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B126" t="n">
@@ -4532,7 +4548,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B127" t="n">
@@ -4561,7 +4577,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B128" t="n">

--- a/output/Data and Chart Outputs/puertorico_generation_monthly.xlsx
+++ b/output/Data and Chart Outputs/puertorico_generation_monthly.xlsx
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="mmm/yy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,11 +61,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -816,6 +815,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -844,6 +844,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -923,7 +924,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B2" t="n">
@@ -952,7 +953,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B3" t="n">
@@ -981,7 +982,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B4" t="n">
@@ -1010,7 +1011,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B5" t="n">
@@ -1039,7 +1040,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B6" t="n">
@@ -1068,7 +1069,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B7" t="n">
@@ -1097,7 +1098,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B8" t="n">
@@ -1126,7 +1127,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B9" t="n">
@@ -1155,7 +1156,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B10" t="n">
@@ -1184,7 +1185,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B11" t="n">
@@ -1213,7 +1214,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B12" t="n">
@@ -1242,7 +1243,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B13" t="n">
@@ -1271,7 +1272,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B14" t="n">
@@ -1300,7 +1301,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B15" t="n">
@@ -1329,7 +1330,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B16" t="n">
@@ -1358,7 +1359,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B17" t="n">
@@ -1387,7 +1388,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B18" t="n">
@@ -1416,7 +1417,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B19" t="n">
@@ -1445,7 +1446,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B20" t="n">
@@ -1474,7 +1475,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B21" t="n">
@@ -1503,7 +1504,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B22" t="n">
@@ -1532,7 +1533,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B23" t="n">
@@ -1561,7 +1562,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B24" t="n">
@@ -1590,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B25" t="n">
@@ -1619,7 +1620,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B26" t="n">
@@ -1648,7 +1649,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B27" t="n">
@@ -1677,7 +1678,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B28" t="n">
@@ -1706,7 +1707,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B29" t="n">
@@ -1735,7 +1736,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B30" t="n">
@@ -1764,7 +1765,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B31" t="n">
@@ -1793,7 +1794,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B32" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B33" t="n">
@@ -1851,7 +1852,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B34" t="n">
@@ -1880,7 +1881,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B35" t="n">
@@ -1909,7 +1910,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B36" t="n">
@@ -1938,7 +1939,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B37" t="n">
@@ -1967,7 +1968,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B38" t="n">
@@ -1996,7 +1997,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B39" t="n">
@@ -2025,7 +2026,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B40" t="n">
@@ -2054,7 +2055,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B41" t="n">
@@ -2083,7 +2084,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B42" t="n">
@@ -2112,7 +2113,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B43" t="n">
@@ -2141,7 +2142,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B44" t="n">
@@ -2170,7 +2171,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B45" t="n">
@@ -2199,7 +2200,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B46" t="n">
@@ -2228,7 +2229,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B47" t="n">
@@ -2257,7 +2258,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B48" t="n">
@@ -2286,7 +2287,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B49" t="n">
@@ -2315,7 +2316,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B50" t="n">
@@ -2344,7 +2345,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B51" t="n">
@@ -2373,7 +2374,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B52" t="n">
@@ -2402,7 +2403,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B53" t="n">
@@ -2431,7 +2432,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B54" t="n">
@@ -2460,7 +2461,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B55" t="n">
@@ -2489,7 +2490,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B56" t="n">
@@ -2518,7 +2519,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B57" t="n">
@@ -2547,7 +2548,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B58" t="n">
@@ -2576,7 +2577,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B59" t="n">
@@ -2605,7 +2606,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B60" t="n">
@@ -2634,7 +2635,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B61" t="n">
@@ -2663,7 +2664,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B62" t="n">
@@ -2692,7 +2693,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B63" t="n">
@@ -2721,7 +2722,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B64" t="n">
@@ -2750,7 +2751,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B65" t="n">
@@ -2779,7 +2780,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B66" t="n">
@@ -2808,7 +2809,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B67" t="n">
@@ -2837,7 +2838,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B68" t="n">
@@ -2866,7 +2867,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B69" t="n">
@@ -2895,7 +2896,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B70" t="n">
@@ -2924,7 +2925,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B71" t="n">
@@ -2953,7 +2954,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B72" t="n">
@@ -2982,7 +2983,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B73" t="n">
@@ -3011,7 +3012,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B74" t="n">
@@ -3040,7 +3041,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B75" t="n">
@@ -3069,7 +3070,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B76" t="n">
@@ -3098,7 +3099,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B77" t="n">
@@ -3127,7 +3128,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B78" t="n">
@@ -3156,7 +3157,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B79" t="n">
@@ -3185,7 +3186,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B80" t="n">
@@ -3214,7 +3215,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B81" t="n">
@@ -3243,7 +3244,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B82" t="n">
@@ -3272,7 +3273,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B83" t="n">
@@ -3301,7 +3302,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B84" t="n">
@@ -3330,7 +3331,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B85" t="n">
@@ -3359,7 +3360,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B86" t="n">
@@ -3388,7 +3389,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B87" t="n">
@@ -3417,7 +3418,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B88" t="n">
@@ -3446,7 +3447,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B89" t="n">
@@ -3475,7 +3476,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B90" t="n">
@@ -3504,7 +3505,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B91" t="n">
@@ -3533,7 +3534,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B92" t="n">
@@ -3562,7 +3563,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B93" t="n">
@@ -3591,7 +3592,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B94" t="n">
@@ -3620,7 +3621,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B95" t="n">
@@ -3649,7 +3650,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B96" t="n">
@@ -3678,7 +3679,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B97" t="n">
@@ -3707,7 +3708,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B98" t="n">
@@ -3736,7 +3737,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B99" t="n">
@@ -3765,7 +3766,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B100" t="n">
@@ -3794,7 +3795,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B101" t="n">
@@ -3823,7 +3824,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B102" t="n">
@@ -3852,7 +3853,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B103" t="n">
@@ -3881,7 +3882,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B104" t="n">
@@ -3910,7 +3911,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B105" t="n">
@@ -3939,7 +3940,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B106" t="n">
@@ -3968,7 +3969,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B107" t="n">
@@ -3997,7 +3998,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B108" t="n">
@@ -4026,7 +4027,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B109" t="n">
@@ -4055,7 +4056,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B110" t="n">
@@ -4084,7 +4085,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B111" t="n">
@@ -4113,7 +4114,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B112" t="n">
@@ -4142,7 +4143,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B113" t="n">
@@ -4171,7 +4172,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B114" t="n">
@@ -4200,7 +4201,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B115" t="n">
@@ -4229,7 +4230,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B116" t="n">
@@ -4258,7 +4259,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B117" t="n">
@@ -4287,7 +4288,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B118" t="n">
@@ -4316,7 +4317,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B119" t="n">
@@ -4345,7 +4346,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B120" t="n">
@@ -4374,7 +4375,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B121" t="n">
@@ -4403,7 +4404,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B122" t="n">
@@ -4432,7 +4433,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B123" t="n">
@@ -4461,7 +4462,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B124" t="n">
@@ -4490,7 +4491,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B125" t="n">
@@ -4519,7 +4520,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B126" t="n">
@@ -4548,7 +4549,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B127" t="n">
@@ -4577,7 +4578,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B128" t="n">

--- a/output/Data and Chart Outputs/puertorico_generation_monthly.xlsx
+++ b/output/Data and Chart Outputs/puertorico_generation_monthly.xlsx
@@ -153,7 +153,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Puerto Rico generation by fuel (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Puerto Rico generation by fuel (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -183,12 +184,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$128</f>
+              <f>'Chart'!$B$2:$B$129</f>
             </numRef>
           </val>
         </ser>
@@ -211,12 +212,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$128</f>
+              <f>'Chart'!$C$2:$C$129</f>
             </numRef>
           </val>
         </ser>
@@ -230,7 +231,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -239,12 +240,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$128</f>
+              <f>'Chart'!$D$2:$D$129</f>
             </numRef>
           </val>
         </ser>
@@ -267,12 +268,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$128</f>
+              <f>'Chart'!$E$2:$E$129</f>
             </numRef>
           </val>
         </ser>
@@ -286,7 +287,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -295,12 +296,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$128</f>
+              <f>'Chart'!$F$2:$F$129</f>
             </numRef>
           </val>
         </ser>
@@ -314,7 +315,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -323,12 +324,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$128</f>
+              <f>'Chart'!$G$2:$G$129</f>
             </numRef>
           </val>
         </ser>
@@ -342,7 +343,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -351,12 +352,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$128</f>
+              <f>'Chart'!$H$2:$H$129</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +380,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$128</f>
+              <f>'Chart'!$A$2:$A$129</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$128</f>
+              <f>'Chart'!$I$2:$I$129</f>
             </numRef>
           </val>
         </ser>
@@ -870,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4060,7 +4061,7 @@
         <v>45658</v>
       </c>
       <c r="B110" t="n">
-        <v>555.35429</v>
+        <v>573.60488</v>
       </c>
       <c r="C110" t="n">
         <v>277.91419</v>
@@ -4069,19 +4070,19 @@
         <v>190.836</v>
       </c>
       <c r="E110" t="n">
-        <v>140.67052</v>
+        <v>150.10063</v>
       </c>
       <c r="F110" t="n">
-        <v>14.39184</v>
+        <v>20.20984</v>
       </c>
       <c r="G110" t="n">
-        <v>15.002</v>
+        <v>15.022</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.344</v>
+        <v>-0.358</v>
       </c>
     </row>
     <row r="111">
@@ -4089,7 +4090,7 @@
         <v>45689</v>
       </c>
       <c r="B111" t="n">
-        <v>444.8452</v>
+        <v>459.48407</v>
       </c>
       <c r="C111" t="n">
         <v>327.82622</v>
@@ -4098,19 +4099,19 @@
         <v>188.689</v>
       </c>
       <c r="E111" t="n">
-        <v>126.41158</v>
+        <v>136.41805</v>
       </c>
       <c r="F111" t="n">
-        <v>15.05972</v>
+        <v>20.39868</v>
       </c>
       <c r="G111" t="n">
-        <v>21.649</v>
+        <v>21.673</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>2.232</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.406</v>
+        <v>-0.419</v>
       </c>
     </row>
     <row r="112">
@@ -4118,7 +4119,7 @@
         <v>45717</v>
       </c>
       <c r="B112" t="n">
-        <v>452.66214</v>
+        <v>467.58732</v>
       </c>
       <c r="C112" t="n">
         <v>186.43787</v>
@@ -4127,19 +4128,19 @@
         <v>330.265</v>
       </c>
       <c r="E112" t="n">
-        <v>221.425</v>
+        <v>231.89923</v>
       </c>
       <c r="F112" t="n">
-        <v>17.87947</v>
+        <v>24.63747</v>
       </c>
       <c r="G112" t="n">
-        <v>13.448</v>
+        <v>13.464</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>5.403</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.789</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="113">
@@ -4147,7 +4148,7 @@
         <v>45748</v>
       </c>
       <c r="B113" t="n">
-        <v>458.6353</v>
+        <v>473.75395</v>
       </c>
       <c r="C113" t="n">
         <v>161.50405</v>
@@ -4156,19 +4157,19 @@
         <v>241.303</v>
       </c>
       <c r="E113" t="n">
-        <v>239.96965</v>
+        <v>250.2303</v>
       </c>
       <c r="F113" t="n">
-        <v>17.15374</v>
+        <v>23.53074</v>
       </c>
       <c r="G113" t="n">
-        <v>15.685</v>
+        <v>15.707</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>4.419</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.466</v>
+        <v>-0.474</v>
       </c>
     </row>
     <row r="114">
@@ -4176,7 +4177,7 @@
         <v>45778</v>
       </c>
       <c r="B114" t="n">
-        <v>603.44453</v>
+        <v>623.24086</v>
       </c>
       <c r="C114" t="n">
         <v>296.2841</v>
@@ -4185,19 +4186,19 @@
         <v>307.555</v>
       </c>
       <c r="E114" t="n">
-        <v>100.79238</v>
+        <v>111.14575</v>
       </c>
       <c r="F114" t="n">
-        <v>17.9132</v>
+        <v>24.42572</v>
       </c>
       <c r="G114" t="n">
-        <v>17.358</v>
+        <v>17.359</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>6.515</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="115">
@@ -4205,7 +4206,7 @@
         <v>45809</v>
       </c>
       <c r="B115" t="n">
-        <v>534.44904</v>
+        <v>551.88886</v>
       </c>
       <c r="C115" t="n">
         <v>387.41096</v>
@@ -4214,19 +4215,19 @@
         <v>283.861</v>
       </c>
       <c r="E115" t="n">
-        <v>150.89101</v>
+        <v>163.87058</v>
       </c>
       <c r="F115" t="n">
-        <v>17.55318</v>
+        <v>24.24218</v>
       </c>
       <c r="G115" t="n">
         <v>26.713</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>3.137</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.269</v>
+        <v>-0.281</v>
       </c>
     </row>
     <row r="116">
@@ -4234,7 +4235,7 @@
         <v>45839</v>
       </c>
       <c r="B116" t="n">
-        <v>614.50681</v>
+        <v>634.6822</v>
       </c>
       <c r="C116" t="n">
         <v>405.67958</v>
@@ -4243,19 +4244,19 @@
         <v>265.21</v>
       </c>
       <c r="E116" t="n">
-        <v>168.35061</v>
+        <v>179.71339</v>
       </c>
       <c r="F116" t="n">
-        <v>18.72066</v>
+        <v>25.58666</v>
       </c>
       <c r="G116" t="n">
-        <v>23.938</v>
+        <v>23.948</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.114</v>
+        <v>-0.125</v>
       </c>
     </row>
     <row r="117">
@@ -4263,7 +4264,7 @@
         <v>45870</v>
       </c>
       <c r="B117" t="n">
-        <v>785.86313</v>
+        <v>811.67228</v>
       </c>
       <c r="C117" t="n">
         <v>301.62061</v>
@@ -4272,19 +4273,19 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>126.84726</v>
+        <v>134.42556</v>
       </c>
       <c r="F117" t="n">
-        <v>18.43434</v>
+        <v>25.24134</v>
       </c>
       <c r="G117" t="n">
-        <v>16.81</v>
+        <v>16.814</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>6.407</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.035</v>
+        <v>-0.043</v>
       </c>
     </row>
     <row r="118">
@@ -4292,7 +4293,7 @@
         <v>45901</v>
       </c>
       <c r="B118" t="n">
-        <v>782.23017</v>
+        <v>807.82938</v>
       </c>
       <c r="C118" t="n">
         <v>296.44984</v>
@@ -4301,19 +4302,19 @@
         <v>283.614</v>
       </c>
       <c r="E118" t="n">
-        <v>95.17400000000001</v>
+        <v>100.98385</v>
       </c>
       <c r="F118" t="n">
-        <v>15.691</v>
+        <v>21.959</v>
       </c>
       <c r="G118" t="n">
-        <v>9.208</v>
+        <v>9.211</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>4.747</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.058</v>
+        <v>-0.066</v>
       </c>
     </row>
     <row r="119">
@@ -4321,7 +4322,7 @@
         <v>45931</v>
       </c>
       <c r="B119" t="n">
-        <v>679.61851</v>
+        <v>699.55007</v>
       </c>
       <c r="C119" t="n">
         <v>461.41729</v>
@@ -4330,19 +4331,19 @@
         <v>150.908</v>
       </c>
       <c r="E119" t="n">
-        <v>202.62521</v>
+        <v>218.35744</v>
       </c>
       <c r="F119" t="n">
-        <v>15.019</v>
+        <v>20.788</v>
       </c>
       <c r="G119" t="n">
-        <v>7.997</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>4.696</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.051</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="120">
@@ -4350,7 +4351,7 @@
         <v>45962</v>
       </c>
       <c r="B120" t="n">
-        <v>602.7464</v>
+        <v>622.55695</v>
       </c>
       <c r="C120" t="n">
         <v>379.32268</v>
@@ -4359,19 +4360,19 @@
         <v>262.924</v>
       </c>
       <c r="E120" t="n">
-        <v>131.18392</v>
+        <v>140.42402</v>
       </c>
       <c r="F120" t="n">
-        <v>15.8261</v>
+        <v>20.8601</v>
       </c>
       <c r="G120" t="n">
-        <v>11.466</v>
+        <v>11.475</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>3.003</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.047</v>
+        <v>-0.055</v>
       </c>
     </row>
     <row r="121">
@@ -4379,7 +4380,7 @@
         <v>45992</v>
       </c>
       <c r="B121" t="n">
-        <v>486.04527</v>
+        <v>501.97811</v>
       </c>
       <c r="C121" t="n">
         <v>471.07686</v>
@@ -4388,19 +4389,19 @@
         <v>273.948</v>
       </c>
       <c r="E121" t="n">
-        <v>69.90688</v>
+        <v>81.78502</v>
       </c>
       <c r="F121" t="n">
-        <v>16.256</v>
+        <v>21.497</v>
       </c>
       <c r="G121" t="n">
-        <v>10.932</v>
+        <v>10.94</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>1.871</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.055</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="122">
@@ -4437,7 +4438,7 @@
         <v>46054</v>
       </c>
       <c r="B123" t="n">
-        <v>556.0905299999999</v>
+        <v>556.08992</v>
       </c>
       <c r="C123" t="n">
         <v>325.04641</v>
@@ -4446,7 +4447,7 @@
         <v>141.62</v>
       </c>
       <c r="E123" t="n">
-        <v>52.25907</v>
+        <v>52.25967</v>
       </c>
       <c r="F123" t="n">
         <v>13.976</v>
@@ -4604,6 +4605,35 @@
       </c>
       <c r="I128" t="n">
         <v>-0.136</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B129" t="n">
+        <v>716.81976</v>
+      </c>
+      <c r="C129" t="n">
+        <v>430.62336</v>
+      </c>
+      <c r="D129" t="n">
+        <v>267.339</v>
+      </c>
+      <c r="E129" t="n">
+        <v>169.83288</v>
+      </c>
+      <c r="F129" t="n">
+        <v>17.82315</v>
+      </c>
+      <c r="G129" t="n">
+        <v>25.919</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-0.012</v>
       </c>
     </row>
   </sheetData>
@@ -4618,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7498,28 +7528,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>712.646</v>
+        <v>725.12203</v>
       </c>
       <c r="C110" t="n">
-        <v>219.88584</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0</v>
+        <v>222.61284</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>0.00023</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1.38589</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="H110" t="n">
-        <v>261.293</v>
+        <v>279.46155</v>
       </c>
       <c r="I110" t="n">
-        <v>1193.82484</v>
+        <v>1228.97954</v>
       </c>
     </row>
     <row r="111">
@@ -7529,28 +7556,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>670.561</v>
+        <v>684.27207</v>
       </c>
       <c r="C111" t="n">
-        <v>224.99172</v>
-      </c>
-      <c r="D111" t="n">
-        <v>0</v>
+        <v>227.25268</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>0.00024</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1.11163</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="H111" t="n">
-        <v>228.522</v>
+        <v>243.3094</v>
       </c>
       <c r="I111" t="n">
-        <v>1124.07472</v>
+        <v>1156.30202</v>
       </c>
     </row>
     <row r="112">
@@ -7560,28 +7584,25 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>583.989</v>
+        <v>601.63687</v>
       </c>
       <c r="C112" t="n">
-        <v>360.80347</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0</v>
+        <v>363.72947</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.00026</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1.13337</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="H112" t="n">
-        <v>276.536</v>
+        <v>291.69492</v>
       </c>
       <c r="I112" t="n">
-        <v>1221.32847</v>
+        <v>1258.89389</v>
       </c>
     </row>
     <row r="113">
@@ -7591,28 +7612,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>594.2859999999999</v>
+        <v>610.60371</v>
       </c>
       <c r="C113" t="n">
-        <v>273.67574</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
+        <v>276.30574</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>0.00025</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1.14806</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H113" t="n">
-        <v>265.823</v>
+        <v>280.98128</v>
       </c>
       <c r="I113" t="n">
-        <v>1133.78474</v>
+        <v>1169.97404</v>
       </c>
     </row>
     <row r="114">
@@ -7622,28 +7640,25 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>728.282</v>
+        <v>746.8163</v>
       </c>
       <c r="C114" t="n">
-        <v>342.3562</v>
-      </c>
-      <c r="D114" t="n">
-        <v>0</v>
+        <v>345.20872</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>0.00025</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1.50327</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="H114" t="n">
-        <v>272.239</v>
+        <v>291.67689</v>
       </c>
       <c r="I114" t="n">
-        <v>1342.8772</v>
+        <v>1386.04543</v>
       </c>
     </row>
     <row r="115">
@@ -7653,28 +7668,25 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>830.756</v>
+        <v>848.37757</v>
       </c>
       <c r="C115" t="n">
-        <v>327.85818</v>
-      </c>
-      <c r="D115" t="n">
-        <v>0</v>
+        <v>330.75218</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1.32432</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.853</v>
       </c>
       <c r="H115" t="n">
-        <v>241.995</v>
+        <v>259.53518</v>
       </c>
       <c r="I115" t="n">
-        <v>1400.60918</v>
+        <v>1440.84257</v>
       </c>
     </row>
     <row r="116">
@@ -7684,28 +7696,25 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>903.9400000000001</v>
+        <v>919.91909</v>
       </c>
       <c r="C116" t="n">
-        <v>307.75466</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0</v>
+        <v>310.89966</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>0.00028</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>1.53205</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="H116" t="n">
-        <v>284.597</v>
+        <v>304.46974</v>
       </c>
       <c r="I116" t="n">
-        <v>1496.29166</v>
+        <v>1537.59482</v>
       </c>
     </row>
     <row r="117">
@@ -7715,28 +7724,25 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>923.105</v>
+        <v>939.0326</v>
       </c>
       <c r="C117" t="n">
-        <v>35.20934</v>
-      </c>
-      <c r="D117" t="n">
-        <v>0</v>
+        <v>38.21634</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1.95986</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="H117" t="n">
-        <v>291.226</v>
+        <v>316.1588</v>
       </c>
       <c r="I117" t="n">
-        <v>1249.54034</v>
+        <v>1296.13779</v>
       </c>
     </row>
     <row r="118">
@@ -7746,28 +7752,25 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>900.08</v>
+        <v>912.31128</v>
       </c>
       <c r="C118" t="n">
-        <v>308.455</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0</v>
+        <v>311.217</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>0.00014</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1.94868</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H118" t="n">
-        <v>273.774</v>
+        <v>298.43397</v>
       </c>
       <c r="I118" t="n">
-        <v>1482.309</v>
+        <v>1524.72807</v>
       </c>
     </row>
     <row r="119">
@@ -7777,28 +7780,25 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1054.966</v>
+        <v>1074.12803</v>
       </c>
       <c r="C119" t="n">
-        <v>173.873</v>
-      </c>
-      <c r="D119" t="n">
-        <v>0</v>
+        <v>176.377</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1.68362</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>0.773</v>
       </c>
       <c r="H119" t="n">
-        <v>288.695</v>
+        <v>310.70281</v>
       </c>
       <c r="I119" t="n">
-        <v>1517.534</v>
+        <v>1563.66479</v>
       </c>
     </row>
     <row r="120">
@@ -7808,28 +7808,25 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>910.529</v>
+        <v>924.16263</v>
       </c>
       <c r="C120" t="n">
-        <v>290.1691</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0</v>
+        <v>292.7261</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>0.00023</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1.50435</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>202.724</v>
+        <v>222.11746</v>
       </c>
       <c r="I120" t="n">
-        <v>1403.4221</v>
+        <v>1440.51077</v>
       </c>
     </row>
     <row r="121">
@@ -7839,28 +7836,25 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>744.489</v>
+        <v>759.45683</v>
       </c>
       <c r="C121" t="n">
-        <v>301.081</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0</v>
+        <v>303.711</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>0.00029</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1.20989</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>282.54</v>
+        <v>298.65497</v>
       </c>
       <c r="I121" t="n">
-        <v>1328.11</v>
+        <v>1363.03298</v>
       </c>
     </row>
     <row r="122">
@@ -7875,9 +7869,6 @@
       <c r="C122" t="n">
         <v>324.925</v>
       </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
@@ -7906,9 +7897,6 @@
       <c r="C123" t="n">
         <v>167.954</v>
       </c>
-      <c r="D123" t="n">
-        <v>0</v>
-      </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
@@ -7937,9 +7925,6 @@
       <c r="C124" t="n">
         <v>270.674</v>
       </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
@@ -8078,6 +8063,37 @@
       </c>
       <c r="I128" t="n">
         <v>1607.53651</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1046</v>
+      </c>
+      <c r="C129" t="n">
+        <v>311.06915</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>271.276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1628.34515</v>
       </c>
     </row>
   </sheetData>
@@ -8091,7 +8107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P128"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8137,40 +8153,35 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>OOG</t>
+          <t>OTH</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>OTH</t>
+          <t>RFO</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>RFO</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>WND</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>WND</t>
+          <t>WOO</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>WOO</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>Total_All_Fuels</t>
         </is>
@@ -8194,19 +8205,19 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8228,19 +8239,19 @@
       <c r="H3" t="n">
         <v>0</v>
       </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8262,19 +8273,19 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8296,19 +8307,19 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8330,19 +8341,19 @@
       <c r="H6" t="n">
         <v>0</v>
       </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8364,19 +8375,19 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8398,19 +8409,19 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8432,19 +8443,19 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8466,19 +8477,19 @@
       <c r="H10" t="n">
         <v>0</v>
       </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8509,6 +8520,9 @@
       <c r="H11" t="n">
         <v>0</v>
       </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
@@ -8521,10 +8535,7 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8555,6 +8566,9 @@
       <c r="H12" t="n">
         <v>0</v>
       </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
@@ -8567,10 +8581,7 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8601,6 +8612,9 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
@@ -8613,10 +8627,7 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8647,22 +8658,22 @@
       <c r="H14" t="n">
         <v>530.77</v>
       </c>
+      <c r="I14" t="n">
+        <v>-0.015</v>
+      </c>
       <c r="J14" t="n">
-        <v>-0.015</v>
+        <v>436.54916</v>
       </c>
       <c r="K14" t="n">
-        <v>436.54916</v>
+        <v>14.664</v>
       </c>
       <c r="L14" t="n">
-        <v>14.664</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
         <v>15.245</v>
       </c>
-      <c r="P14" t="n">
+      <c r="O14" t="n">
         <v>1296.17492</v>
       </c>
     </row>
@@ -8693,22 +8704,22 @@
       <c r="H15" t="n">
         <v>445.50977</v>
       </c>
+      <c r="I15" t="n">
+        <v>-0.016</v>
+      </c>
       <c r="J15" t="n">
-        <v>-0.016</v>
+        <v>500.49495</v>
       </c>
       <c r="K15" t="n">
-        <v>500.49495</v>
+        <v>14.449</v>
       </c>
       <c r="L15" t="n">
-        <v>14.449</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
         <v>13.373</v>
       </c>
-      <c r="P15" t="n">
+      <c r="O15" t="n">
         <v>1193.4123</v>
       </c>
     </row>
@@ -8739,22 +8750,22 @@
       <c r="H16" t="n">
         <v>470.26343</v>
       </c>
+      <c r="I16" t="n">
+        <v>0.005</v>
+      </c>
       <c r="J16" t="n">
-        <v>0.005</v>
+        <v>479.28602</v>
       </c>
       <c r="K16" t="n">
-        <v>479.28602</v>
+        <v>15.392</v>
       </c>
       <c r="L16" t="n">
-        <v>15.392</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
         <v>20.133</v>
       </c>
-      <c r="P16" t="n">
+      <c r="O16" t="n">
         <v>1323.67409</v>
       </c>
     </row>
@@ -8785,22 +8796,22 @@
       <c r="H17" t="n">
         <v>478.67062</v>
       </c>
+      <c r="I17" t="n">
+        <v>0.006</v>
+      </c>
       <c r="J17" t="n">
-        <v>0.006</v>
+        <v>454.74694</v>
       </c>
       <c r="K17" t="n">
-        <v>454.74694</v>
+        <v>15.639</v>
       </c>
       <c r="L17" t="n">
-        <v>15.639</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
         <v>14.792</v>
       </c>
-      <c r="P17" t="n">
+      <c r="O17" t="n">
         <v>1308.25719</v>
       </c>
     </row>
@@ -8831,22 +8842,22 @@
       <c r="H18" t="n">
         <v>453.67319</v>
       </c>
+      <c r="I18" t="n">
+        <v>-0.012</v>
+      </c>
       <c r="J18" t="n">
-        <v>-0.012</v>
+        <v>575.25541</v>
       </c>
       <c r="K18" t="n">
-        <v>575.25541</v>
+        <v>16.396</v>
       </c>
       <c r="L18" t="n">
-        <v>16.396</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
         <v>18.489</v>
       </c>
-      <c r="P18" t="n">
+      <c r="O18" t="n">
         <v>1429.89552</v>
       </c>
     </row>
@@ -8877,22 +8888,22 @@
       <c r="H19" t="n">
         <v>566.01369</v>
       </c>
+      <c r="I19" t="n">
+        <v>-0.015</v>
+      </c>
       <c r="J19" t="n">
-        <v>-0.015</v>
+        <v>386.09812</v>
       </c>
       <c r="K19" t="n">
-        <v>386.09812</v>
+        <v>16.107</v>
       </c>
       <c r="L19" t="n">
-        <v>16.107</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
         <v>24.036</v>
       </c>
-      <c r="P19" t="n">
+      <c r="O19" t="n">
         <v>1442.08918</v>
       </c>
     </row>
@@ -8923,22 +8934,22 @@
       <c r="H20" t="n">
         <v>598.79296</v>
       </c>
+      <c r="I20" t="n">
+        <v>-0.012</v>
+      </c>
       <c r="J20" t="n">
-        <v>-0.012</v>
+        <v>399.17018</v>
       </c>
       <c r="K20" t="n">
-        <v>399.17018</v>
+        <v>16.305</v>
       </c>
       <c r="L20" t="n">
-        <v>16.305</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
         <v>20.236</v>
       </c>
-      <c r="P20" t="n">
+      <c r="O20" t="n">
         <v>1487.31567</v>
       </c>
     </row>
@@ -8969,22 +8980,22 @@
       <c r="H21" t="n">
         <v>604.55996</v>
       </c>
+      <c r="I21" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="J21" t="n">
-        <v>-0.018</v>
+        <v>490.25682</v>
       </c>
       <c r="K21" t="n">
-        <v>490.25682</v>
+        <v>15.365</v>
       </c>
       <c r="L21" t="n">
-        <v>15.365</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
         <v>19.396</v>
       </c>
-      <c r="P21" t="n">
+      <c r="O21" t="n">
         <v>1573.08172</v>
       </c>
     </row>
@@ -9015,22 +9026,22 @@
       <c r="H22" t="n">
         <v>266.93088</v>
       </c>
+      <c r="I22" t="n">
+        <v>-0.005</v>
+      </c>
       <c r="J22" t="n">
-        <v>-0.005</v>
+        <v>349.59193</v>
       </c>
       <c r="K22" t="n">
-        <v>349.59193</v>
+        <v>7.01</v>
       </c>
       <c r="L22" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
         <v>2.327</v>
       </c>
-      <c r="P22" t="n">
+      <c r="O22" t="n">
         <v>791.47128</v>
       </c>
     </row>
@@ -9061,11 +9072,14 @@
       <c r="H23" t="n">
         <v>61.37602</v>
       </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>44.50119</v>
       </c>
       <c r="K23" t="n">
-        <v>44.50119</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9073,10 +9087,7 @@
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="O23" t="n">
         <v>273.60401</v>
       </c>
     </row>
@@ -9107,11 +9118,14 @@
       <c r="H24" t="n">
         <v>255.30473</v>
       </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>172.00964</v>
       </c>
       <c r="K24" t="n">
-        <v>172.00964</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -9119,10 +9133,7 @@
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="O24" t="n">
         <v>610.15286</v>
       </c>
     </row>
@@ -9153,11 +9164,14 @@
       <c r="H25" t="n">
         <v>308.98469</v>
       </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>328.5397</v>
       </c>
       <c r="K25" t="n">
-        <v>328.5397</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -9165,10 +9179,7 @@
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="O25" t="n">
         <v>819.93822</v>
       </c>
     </row>
@@ -9199,11 +9210,14 @@
       <c r="H26" t="n">
         <v>390.884</v>
       </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>405.11293</v>
       </c>
       <c r="K26" t="n">
-        <v>405.11293</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9211,10 +9225,7 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="O26" t="n">
         <v>1048.862</v>
       </c>
     </row>
@@ -9245,22 +9256,22 @@
       <c r="H27" t="n">
         <v>328.65947</v>
       </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>402.43969</v>
       </c>
       <c r="K27" t="n">
-        <v>402.43969</v>
+        <v>0.054</v>
       </c>
       <c r="L27" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
         <v>1.331</v>
       </c>
-      <c r="P27" t="n">
+      <c r="O27" t="n">
         <v>1003.80719</v>
       </c>
     </row>
@@ -9291,22 +9302,22 @@
       <c r="H28" t="n">
         <v>454.16832</v>
       </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>149.51404</v>
       </c>
       <c r="K28" t="n">
-        <v>149.51404</v>
+        <v>0.585</v>
       </c>
       <c r="L28" t="n">
-        <v>0.585</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
         <v>2.031</v>
       </c>
-      <c r="P28" t="n">
+      <c r="O28" t="n">
         <v>1001.05231</v>
       </c>
     </row>
@@ -9337,22 +9348,22 @@
       <c r="H29" t="n">
         <v>420.26</v>
       </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>110.34933</v>
       </c>
       <c r="K29" t="n">
-        <v>110.34933</v>
+        <v>1.12562</v>
       </c>
       <c r="L29" t="n">
-        <v>1.12562</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
         <v>4.845</v>
       </c>
-      <c r="P29" t="n">
+      <c r="O29" t="n">
         <v>1063.81535</v>
       </c>
     </row>
@@ -9383,22 +9394,22 @@
       <c r="H30" t="n">
         <v>521.96</v>
       </c>
+      <c r="I30" t="n">
+        <v>-0.001</v>
+      </c>
       <c r="J30" t="n">
-        <v>-0.001</v>
+        <v>256.92496</v>
       </c>
       <c r="K30" t="n">
-        <v>256.92496</v>
+        <v>2.053</v>
       </c>
       <c r="L30" t="n">
-        <v>2.053</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
         <v>10.431</v>
       </c>
-      <c r="P30" t="n">
+      <c r="O30" t="n">
         <v>1075.94637</v>
       </c>
     </row>
@@ -9429,22 +9440,22 @@
       <c r="H31" t="n">
         <v>586.06461</v>
       </c>
+      <c r="I31" t="n">
+        <v>-0.019</v>
+      </c>
       <c r="J31" t="n">
-        <v>-0.019</v>
+        <v>123.27696</v>
       </c>
       <c r="K31" t="n">
-        <v>123.27696</v>
+        <v>4.25793</v>
       </c>
       <c r="L31" t="n">
-        <v>4.25793</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
         <v>12.703</v>
       </c>
-      <c r="P31" t="n">
+      <c r="O31" t="n">
         <v>1139.12515</v>
       </c>
     </row>
@@ -9475,22 +9486,22 @@
       <c r="H32" t="n">
         <v>539.0119999999999</v>
       </c>
+      <c r="I32" t="n">
+        <v>-0.042</v>
+      </c>
       <c r="J32" t="n">
-        <v>-0.042</v>
+        <v>146.73771</v>
       </c>
       <c r="K32" t="n">
-        <v>146.73771</v>
+        <v>6.58575</v>
       </c>
       <c r="L32" t="n">
-        <v>6.58575</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
         <v>18.743</v>
       </c>
-      <c r="P32" t="n">
+      <c r="O32" t="n">
         <v>1234.03162</v>
       </c>
     </row>
@@ -9521,22 +9532,22 @@
       <c r="H33" t="n">
         <v>547.62225</v>
       </c>
+      <c r="I33" t="n">
+        <v>-0.174</v>
+      </c>
       <c r="J33" t="n">
-        <v>-0.174</v>
+        <v>158.9783</v>
       </c>
       <c r="K33" t="n">
-        <v>158.9783</v>
+        <v>7.14941</v>
       </c>
       <c r="L33" t="n">
-        <v>7.14941</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
         <v>18.297</v>
       </c>
-      <c r="P33" t="n">
+      <c r="O33" t="n">
         <v>1293.13237</v>
       </c>
     </row>
@@ -9567,22 +9578,22 @@
       <c r="H34" t="n">
         <v>629.067</v>
       </c>
+      <c r="I34" t="n">
+        <v>-0.107</v>
+      </c>
       <c r="J34" t="n">
-        <v>-0.107</v>
+        <v>365.71351</v>
       </c>
       <c r="K34" t="n">
-        <v>365.71351</v>
+        <v>7.44664</v>
       </c>
       <c r="L34" t="n">
-        <v>7.44664</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
         <v>10.731</v>
       </c>
-      <c r="P34" t="n">
+      <c r="O34" t="n">
         <v>1513.40288</v>
       </c>
     </row>
@@ -9613,22 +9624,22 @@
       <c r="H35" t="n">
         <v>650.034</v>
       </c>
+      <c r="I35" t="n">
+        <v>-0.08699999999999999</v>
+      </c>
       <c r="J35" t="n">
-        <v>-0.08699999999999999</v>
+        <v>399.30838</v>
       </c>
       <c r="K35" t="n">
-        <v>399.30838</v>
+        <v>7.94911</v>
       </c>
       <c r="L35" t="n">
-        <v>7.94911</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
         <v>5.98</v>
       </c>
-      <c r="P35" t="n">
+      <c r="O35" t="n">
         <v>1494.81702</v>
       </c>
     </row>
@@ -9659,22 +9670,22 @@
       <c r="H36" t="n">
         <v>538.14352</v>
       </c>
+      <c r="I36" t="n">
+        <v>-0.167</v>
+      </c>
       <c r="J36" t="n">
-        <v>-0.167</v>
+        <v>412.29201</v>
       </c>
       <c r="K36" t="n">
-        <v>412.29201</v>
+        <v>10.50533</v>
       </c>
       <c r="L36" t="n">
-        <v>10.50533</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
         <v>8.904999999999999</v>
       </c>
-      <c r="P36" t="n">
+      <c r="O36" t="n">
         <v>1411.59149</v>
       </c>
     </row>
@@ -9705,22 +9716,22 @@
       <c r="H37" t="n">
         <v>480.333</v>
       </c>
+      <c r="I37" t="n">
+        <v>-0.203</v>
+      </c>
       <c r="J37" t="n">
-        <v>-0.203</v>
+        <v>405.60382</v>
       </c>
       <c r="K37" t="n">
-        <v>405.60382</v>
+        <v>13.46854</v>
       </c>
       <c r="L37" t="n">
-        <v>13.46854</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
         <v>12.87</v>
       </c>
-      <c r="P37" t="n">
+      <c r="O37" t="n">
         <v>1388.98853</v>
       </c>
     </row>
@@ -9751,22 +9762,22 @@
       <c r="H38" t="n">
         <v>591.802</v>
       </c>
+      <c r="I38" t="n">
+        <v>0.09071</v>
+      </c>
       <c r="J38" t="n">
-        <v>0.09071</v>
+        <v>257.28162</v>
       </c>
       <c r="K38" t="n">
-        <v>257.28162</v>
+        <v>18.91826</v>
       </c>
       <c r="L38" t="n">
-        <v>18.91826</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
         <v>10.875</v>
       </c>
-      <c r="P38" t="n">
+      <c r="O38" t="n">
         <v>1329.85868</v>
       </c>
     </row>
@@ -9797,22 +9808,22 @@
       <c r="H39" t="n">
         <v>534.617</v>
       </c>
+      <c r="I39" t="n">
+        <v>-0.13148</v>
+      </c>
       <c r="J39" t="n">
-        <v>-0.13148</v>
+        <v>257.33075</v>
       </c>
       <c r="K39" t="n">
-        <v>257.33075</v>
+        <v>18.70038</v>
       </c>
       <c r="L39" t="n">
-        <v>18.70038</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
         <v>12.856</v>
       </c>
-      <c r="P39" t="n">
+      <c r="O39" t="n">
         <v>1238.02799</v>
       </c>
     </row>
@@ -9843,22 +9854,22 @@
       <c r="H40" t="n">
         <v>628.604</v>
       </c>
+      <c r="I40" t="n">
+        <v>-0.2682</v>
+      </c>
       <c r="J40" t="n">
-        <v>-0.2682</v>
+        <v>272.79329</v>
       </c>
       <c r="K40" t="n">
-        <v>272.79329</v>
+        <v>22.6267</v>
       </c>
       <c r="L40" t="n">
-        <v>22.6267</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
         <v>14.532</v>
       </c>
-      <c r="P40" t="n">
+      <c r="O40" t="n">
         <v>1422.2684</v>
       </c>
     </row>
@@ -9889,22 +9900,22 @@
       <c r="H41" t="n">
         <v>614.39636</v>
       </c>
+      <c r="I41" t="n">
+        <v>-0.32904</v>
+      </c>
       <c r="J41" t="n">
-        <v>-0.32904</v>
+        <v>331.61834</v>
       </c>
       <c r="K41" t="n">
-        <v>331.61834</v>
+        <v>24.51313</v>
       </c>
       <c r="L41" t="n">
-        <v>24.51313</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
         <v>18.421</v>
       </c>
-      <c r="P41" t="n">
+      <c r="O41" t="n">
         <v>1431.9267</v>
       </c>
     </row>
@@ -9935,22 +9946,22 @@
       <c r="H42" t="n">
         <v>644.521</v>
       </c>
+      <c r="I42" t="n">
+        <v>-0.35041</v>
+      </c>
       <c r="J42" t="n">
-        <v>-0.35041</v>
+        <v>290.77695</v>
       </c>
       <c r="K42" t="n">
-        <v>290.77695</v>
+        <v>22.89204</v>
       </c>
       <c r="L42" t="n">
-        <v>22.89204</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
         <v>14.862</v>
       </c>
-      <c r="P42" t="n">
+      <c r="O42" t="n">
         <v>1547.99951</v>
       </c>
     </row>
@@ -9981,22 +9992,22 @@
       <c r="H43" t="n">
         <v>658.0346</v>
       </c>
+      <c r="I43" t="n">
+        <v>-0.35182</v>
+      </c>
       <c r="J43" t="n">
-        <v>-0.35182</v>
+        <v>327.67247</v>
       </c>
       <c r="K43" t="n">
-        <v>327.67247</v>
+        <v>25.72966</v>
       </c>
       <c r="L43" t="n">
-        <v>25.72966</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
         <v>18.386</v>
       </c>
-      <c r="P43" t="n">
+      <c r="O43" t="n">
         <v>1602.02583</v>
       </c>
     </row>
@@ -10027,22 +10038,22 @@
       <c r="H44" t="n">
         <v>623.042</v>
       </c>
+      <c r="I44" t="n">
+        <v>-0.36534</v>
+      </c>
       <c r="J44" t="n">
-        <v>-0.36534</v>
+        <v>269.07476</v>
       </c>
       <c r="K44" t="n">
-        <v>269.07476</v>
+        <v>25.49128</v>
       </c>
       <c r="L44" t="n">
-        <v>25.49128</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
         <v>20.055</v>
       </c>
-      <c r="P44" t="n">
+      <c r="O44" t="n">
         <v>1648.97606</v>
       </c>
     </row>
@@ -10073,22 +10084,22 @@
       <c r="H45" t="n">
         <v>536.4650799999999</v>
       </c>
+      <c r="I45" t="n">
+        <v>-0.30789</v>
+      </c>
       <c r="J45" t="n">
-        <v>-0.30789</v>
+        <v>335.35646</v>
       </c>
       <c r="K45" t="n">
-        <v>335.35646</v>
+        <v>23.58305</v>
       </c>
       <c r="L45" t="n">
-        <v>23.58305</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
         <v>16.228</v>
       </c>
-      <c r="P45" t="n">
+      <c r="O45" t="n">
         <v>1679.35569</v>
       </c>
     </row>
@@ -10119,22 +10130,22 @@
       <c r="H46" t="n">
         <v>599.485</v>
       </c>
+      <c r="I46" t="n">
+        <v>-0.20573</v>
+      </c>
       <c r="J46" t="n">
-        <v>-0.20573</v>
+        <v>302.91629</v>
       </c>
       <c r="K46" t="n">
-        <v>302.91629</v>
+        <v>21.27796</v>
       </c>
       <c r="L46" t="n">
-        <v>21.27796</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
         <v>7.066</v>
       </c>
-      <c r="P46" t="n">
+      <c r="O46" t="n">
         <v>1618.27808</v>
       </c>
     </row>
@@ -10165,22 +10176,22 @@
       <c r="H47" t="n">
         <v>637.174</v>
       </c>
+      <c r="I47" t="n">
+        <v>-0.21765</v>
+      </c>
       <c r="J47" t="n">
-        <v>-0.21765</v>
+        <v>412.98463</v>
       </c>
       <c r="K47" t="n">
-        <v>412.98463</v>
+        <v>23.34744</v>
       </c>
       <c r="L47" t="n">
-        <v>23.34744</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
         <v>6.489</v>
       </c>
-      <c r="P47" t="n">
+      <c r="O47" t="n">
         <v>1631.63192</v>
       </c>
     </row>
@@ -10211,22 +10222,22 @@
       <c r="H48" t="n">
         <v>649.481</v>
       </c>
+      <c r="I48" t="n">
+        <v>-0.21823</v>
+      </c>
       <c r="J48" t="n">
-        <v>-0.21823</v>
+        <v>355.57509</v>
       </c>
       <c r="K48" t="n">
-        <v>355.57509</v>
+        <v>23.32665</v>
       </c>
       <c r="L48" t="n">
-        <v>23.32665</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
         <v>6.146</v>
       </c>
-      <c r="P48" t="n">
+      <c r="O48" t="n">
         <v>1507.86342</v>
       </c>
     </row>
@@ -10257,22 +10268,22 @@
       <c r="H49" t="n">
         <v>642.053</v>
       </c>
+      <c r="I49" t="n">
+        <v>-0.18991</v>
+      </c>
       <c r="J49" t="n">
-        <v>-0.18991</v>
+        <v>351.89298</v>
       </c>
       <c r="K49" t="n">
-        <v>351.89298</v>
+        <v>22.00406</v>
       </c>
       <c r="L49" t="n">
-        <v>22.00406</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
         <v>10.194</v>
       </c>
-      <c r="P49" t="n">
+      <c r="O49" t="n">
         <v>1507.97506</v>
       </c>
     </row>
@@ -10303,22 +10314,22 @@
       <c r="H50" t="n">
         <v>197.553</v>
       </c>
+      <c r="I50" t="n">
+        <v>-0.14047</v>
+      </c>
       <c r="J50" t="n">
-        <v>-0.14047</v>
+        <v>389.66945</v>
       </c>
       <c r="K50" t="n">
-        <v>389.66945</v>
+        <v>16.76278</v>
       </c>
       <c r="L50" t="n">
-        <v>16.76278</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
         <v>5.149</v>
       </c>
-      <c r="P50" t="n">
+      <c r="O50" t="n">
         <v>1264.25422</v>
       </c>
     </row>
@@ -10349,22 +10360,22 @@
       <c r="H51" t="n">
         <v>173.037</v>
       </c>
+      <c r="I51" t="n">
+        <v>-0.20884</v>
+      </c>
       <c r="J51" t="n">
-        <v>-0.20884</v>
+        <v>427.6183</v>
       </c>
       <c r="K51" t="n">
-        <v>427.6183</v>
+        <v>22.40698</v>
       </c>
       <c r="L51" t="n">
-        <v>22.40698</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
         <v>13.656</v>
       </c>
-      <c r="P51" t="n">
+      <c r="O51" t="n">
         <v>1344.39218</v>
       </c>
     </row>
@@ -10395,22 +10406,22 @@
       <c r="H52" t="n">
         <v>285.779</v>
       </c>
+      <c r="I52" t="n">
+        <v>-0.20277</v>
+      </c>
       <c r="J52" t="n">
-        <v>-0.20277</v>
+        <v>468.52246</v>
       </c>
       <c r="K52" t="n">
-        <v>468.52246</v>
+        <v>24.5094</v>
       </c>
       <c r="L52" t="n">
-        <v>24.5094</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
         <v>11.211</v>
       </c>
-      <c r="P52" t="n">
+      <c r="O52" t="n">
         <v>1375.21686</v>
       </c>
     </row>
@@ -10441,22 +10452,22 @@
       <c r="H53" t="n">
         <v>380.05899</v>
       </c>
+      <c r="I53" t="n">
+        <v>-0.18051</v>
+      </c>
       <c r="J53" t="n">
-        <v>-0.18051</v>
+        <v>439.9843</v>
       </c>
       <c r="K53" t="n">
-        <v>439.9843</v>
+        <v>26.88882</v>
       </c>
       <c r="L53" t="n">
-        <v>26.88882</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
         <v>12.928</v>
       </c>
-      <c r="P53" t="n">
+      <c r="O53" t="n">
         <v>1425.05828</v>
       </c>
     </row>
@@ -10487,22 +10498,22 @@
       <c r="H54" t="n">
         <v>349.86601</v>
       </c>
+      <c r="I54" t="n">
+        <v>-0.43614</v>
+      </c>
       <c r="J54" t="n">
-        <v>-0.43614</v>
+        <v>445.11458</v>
       </c>
       <c r="K54" t="n">
-        <v>445.11458</v>
+        <v>27.55798</v>
       </c>
       <c r="L54" t="n">
-        <v>27.55798</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
         <v>15.986</v>
       </c>
-      <c r="P54" t="n">
+      <c r="O54" t="n">
         <v>1558.01439</v>
       </c>
     </row>
@@ -10533,22 +10544,22 @@
       <c r="H55" t="n">
         <v>390.81389</v>
       </c>
+      <c r="I55" t="n">
+        <v>-0.38173</v>
+      </c>
       <c r="J55" t="n">
-        <v>-0.38173</v>
+        <v>646.18607</v>
       </c>
       <c r="K55" t="n">
-        <v>646.18607</v>
+        <v>26.63574</v>
       </c>
       <c r="L55" t="n">
-        <v>26.63574</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
         <v>17.668</v>
       </c>
-      <c r="P55" t="n">
+      <c r="O55" t="n">
         <v>1640.77128</v>
       </c>
     </row>
@@ -10579,22 +10590,22 @@
       <c r="H56" t="n">
         <v>476.69379</v>
       </c>
+      <c r="I56" t="n">
+        <v>-0.35461</v>
+      </c>
       <c r="J56" t="n">
-        <v>-0.35461</v>
+        <v>694.57217</v>
       </c>
       <c r="K56" t="n">
-        <v>694.57217</v>
+        <v>25.51393</v>
       </c>
       <c r="L56" t="n">
-        <v>25.51393</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
         <v>19.455</v>
       </c>
-      <c r="P56" t="n">
+      <c r="O56" t="n">
         <v>1668.88479</v>
       </c>
     </row>
@@ -10625,22 +10636,22 @@
       <c r="H57" t="n">
         <v>656.1959900000001</v>
       </c>
+      <c r="I57" t="n">
+        <v>-0.23083</v>
+      </c>
       <c r="J57" t="n">
-        <v>-0.23083</v>
+        <v>541.89958</v>
       </c>
       <c r="K57" t="n">
-        <v>541.89958</v>
+        <v>26.44225</v>
       </c>
       <c r="L57" t="n">
-        <v>26.44225</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
         <v>14.887</v>
       </c>
-      <c r="P57" t="n">
+      <c r="O57" t="n">
         <v>1761.16532</v>
       </c>
     </row>
@@ -10671,22 +10682,22 @@
       <c r="H58" t="n">
         <v>748.10654</v>
       </c>
+      <c r="I58" t="n">
+        <v>-0.20289</v>
+      </c>
       <c r="J58" t="n">
-        <v>-0.20289</v>
+        <v>463.65281</v>
       </c>
       <c r="K58" t="n">
-        <v>463.65281</v>
+        <v>24.19052</v>
       </c>
       <c r="L58" t="n">
-        <v>24.19052</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
         <v>7.326</v>
       </c>
-      <c r="P58" t="n">
+      <c r="O58" t="n">
         <v>1637.59847</v>
       </c>
     </row>
@@ -10717,22 +10728,22 @@
       <c r="H59" t="n">
         <v>709.0658100000001</v>
       </c>
+      <c r="I59" t="n">
+        <v>-0.22683</v>
+      </c>
       <c r="J59" t="n">
-        <v>-0.22683</v>
+        <v>368.26417</v>
       </c>
       <c r="K59" t="n">
-        <v>368.26417</v>
+        <v>23.22075</v>
       </c>
       <c r="L59" t="n">
-        <v>23.22075</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
         <v>9.327999999999999</v>
       </c>
-      <c r="P59" t="n">
+      <c r="O59" t="n">
         <v>1603.18122</v>
       </c>
     </row>
@@ -10763,22 +10774,22 @@
       <c r="H60" t="n">
         <v>615.02086</v>
       </c>
+      <c r="I60" t="n">
+        <v>-0.1703</v>
+      </c>
       <c r="J60" t="n">
-        <v>-0.1703</v>
+        <v>395.70053</v>
       </c>
       <c r="K60" t="n">
-        <v>395.70053</v>
+        <v>19.9954</v>
       </c>
       <c r="L60" t="n">
-        <v>19.9954</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
         <v>7.753</v>
       </c>
-      <c r="P60" t="n">
+      <c r="O60" t="n">
         <v>1477.19136</v>
       </c>
     </row>
@@ -10809,22 +10820,22 @@
       <c r="H61" t="n">
         <v>644.91835</v>
       </c>
+      <c r="I61" t="n">
+        <v>-0.16109</v>
+      </c>
       <c r="J61" t="n">
-        <v>-0.16109</v>
+        <v>400.33681</v>
       </c>
       <c r="K61" t="n">
-        <v>400.33681</v>
+        <v>22.6341</v>
       </c>
       <c r="L61" t="n">
-        <v>22.6341</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
         <v>6.887</v>
       </c>
-      <c r="P61" t="n">
+      <c r="O61" t="n">
         <v>1460.1492</v>
       </c>
     </row>
@@ -10855,22 +10866,22 @@
       <c r="H62" t="n">
         <v>676.10772</v>
       </c>
+      <c r="I62" t="n">
+        <v>-0.22132</v>
+      </c>
       <c r="J62" t="n">
-        <v>-0.22132</v>
+        <v>332.60518</v>
       </c>
       <c r="K62" t="n">
-        <v>332.60518</v>
+        <v>23.6563</v>
       </c>
       <c r="L62" t="n">
-        <v>23.6563</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
         <v>10.126</v>
       </c>
-      <c r="P62" t="n">
+      <c r="O62" t="n">
         <v>1402.09521</v>
       </c>
     </row>
@@ -10901,22 +10912,22 @@
       <c r="H63" t="n">
         <v>649.49116</v>
       </c>
+      <c r="I63" t="n">
+        <v>-0.23982</v>
+      </c>
       <c r="J63" t="n">
-        <v>-0.23982</v>
+        <v>207.06889</v>
       </c>
       <c r="K63" t="n">
-        <v>207.06889</v>
+        <v>24.12582</v>
       </c>
       <c r="L63" t="n">
-        <v>24.12582</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
         <v>17.186</v>
       </c>
-      <c r="P63" t="n">
+      <c r="O63" t="n">
         <v>1303.85126</v>
       </c>
     </row>
@@ -10947,22 +10958,22 @@
       <c r="H64" t="n">
         <v>700.18151</v>
       </c>
+      <c r="I64" t="n">
+        <v>-0.22077</v>
+      </c>
       <c r="J64" t="n">
-        <v>-0.22077</v>
+        <v>257.69789</v>
       </c>
       <c r="K64" t="n">
-        <v>257.69789</v>
+        <v>30.22275</v>
       </c>
       <c r="L64" t="n">
-        <v>30.22275</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
         <v>15.473</v>
       </c>
-      <c r="P64" t="n">
+      <c r="O64" t="n">
         <v>1456.96207</v>
       </c>
     </row>
@@ -10993,22 +11004,22 @@
       <c r="H65" t="n">
         <v>625.186</v>
       </c>
+      <c r="I65" t="n">
+        <v>-0.16514</v>
+      </c>
       <c r="J65" t="n">
-        <v>-0.16514</v>
+        <v>381.41663</v>
       </c>
       <c r="K65" t="n">
-        <v>381.41663</v>
+        <v>27.59782</v>
       </c>
       <c r="L65" t="n">
-        <v>27.59782</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
         <v>12.484</v>
       </c>
-      <c r="P65" t="n">
+      <c r="O65" t="n">
         <v>1464.19156</v>
       </c>
     </row>
@@ -11039,22 +11050,22 @@
       <c r="H66" t="n">
         <v>706.87117</v>
       </c>
+      <c r="I66" t="n">
+        <v>-0.24038</v>
+      </c>
       <c r="J66" t="n">
-        <v>-0.24038</v>
+        <v>406.03941</v>
       </c>
       <c r="K66" t="n">
-        <v>406.03941</v>
+        <v>28.87561</v>
       </c>
       <c r="L66" t="n">
-        <v>28.87561</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
         <v>17.922</v>
       </c>
-      <c r="P66" t="n">
+      <c r="O66" t="n">
         <v>1597.94842</v>
       </c>
     </row>
@@ -11085,22 +11096,22 @@
       <c r="H67" t="n">
         <v>864.00762</v>
       </c>
+      <c r="I67" t="n">
+        <v>-0.25499</v>
+      </c>
       <c r="J67" t="n">
-        <v>-0.25499</v>
+        <v>305.55632</v>
       </c>
       <c r="K67" t="n">
-        <v>305.55632</v>
+        <v>25.25956</v>
       </c>
       <c r="L67" t="n">
-        <v>25.25956</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
         <v>17.297</v>
       </c>
-      <c r="P67" t="n">
+      <c r="O67" t="n">
         <v>1541.43376</v>
       </c>
     </row>
@@ -11131,22 +11142,22 @@
       <c r="H68" t="n">
         <v>942.72354</v>
       </c>
+      <c r="I68" t="n">
+        <v>-0.22008</v>
+      </c>
       <c r="J68" t="n">
-        <v>-0.22008</v>
+        <v>337.28275</v>
       </c>
       <c r="K68" t="n">
-        <v>337.28275</v>
+        <v>25.88183</v>
       </c>
       <c r="L68" t="n">
-        <v>25.88183</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
         <v>22.618</v>
       </c>
-      <c r="P68" t="n">
+      <c r="O68" t="n">
         <v>1691.67835</v>
       </c>
     </row>
@@ -11177,22 +11188,22 @@
       <c r="H69" t="n">
         <v>869.21218</v>
       </c>
+      <c r="I69" t="n">
+        <v>-0.21742</v>
+      </c>
       <c r="J69" t="n">
-        <v>-0.21742</v>
+        <v>423.56461</v>
       </c>
       <c r="K69" t="n">
-        <v>423.56461</v>
+        <v>28.14338</v>
       </c>
       <c r="L69" t="n">
-        <v>28.14338</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
         <v>16.325</v>
       </c>
-      <c r="P69" t="n">
+      <c r="O69" t="n">
         <v>1760.7914</v>
       </c>
     </row>
@@ -11223,22 +11234,22 @@
       <c r="H70" t="n">
         <v>636.2306599999999</v>
       </c>
+      <c r="I70" t="n">
+        <v>-0.24681</v>
+      </c>
       <c r="J70" t="n">
-        <v>-0.24681</v>
+        <v>451.77352</v>
       </c>
       <c r="K70" t="n">
-        <v>451.77352</v>
+        <v>25.73041</v>
       </c>
       <c r="L70" t="n">
-        <v>25.73041</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
         <v>7.394</v>
       </c>
-      <c r="P70" t="n">
+      <c r="O70" t="n">
         <v>1664.87976</v>
       </c>
     </row>
@@ -11269,22 +11280,22 @@
       <c r="H71" t="n">
         <v>612.43444</v>
       </c>
+      <c r="I71" t="n">
+        <v>-0.1323</v>
+      </c>
       <c r="J71" t="n">
-        <v>-0.1323</v>
+        <v>455.92211</v>
       </c>
       <c r="K71" t="n">
-        <v>455.92211</v>
+        <v>22.74876</v>
       </c>
       <c r="L71" t="n">
-        <v>22.74876</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
         <v>8.013</v>
       </c>
-      <c r="P71" t="n">
+      <c r="O71" t="n">
         <v>1649.02406</v>
       </c>
     </row>
@@ -11315,22 +11326,22 @@
       <c r="H72" t="n">
         <v>281.51775</v>
       </c>
+      <c r="I72" t="n">
+        <v>-0.15297</v>
+      </c>
       <c r="J72" t="n">
-        <v>-0.15297</v>
+        <v>670.5499600000001</v>
       </c>
       <c r="K72" t="n">
-        <v>670.5499600000001</v>
+        <v>21.85697</v>
       </c>
       <c r="L72" t="n">
-        <v>21.85697</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
         <v>9.01</v>
       </c>
-      <c r="P72" t="n">
+      <c r="O72" t="n">
         <v>1553.39125</v>
       </c>
     </row>
@@ -11361,22 +11372,22 @@
       <c r="H73" t="n">
         <v>380.43371</v>
       </c>
+      <c r="I73" t="n">
+        <v>-0.13699</v>
+      </c>
       <c r="J73" t="n">
-        <v>-0.13699</v>
+        <v>558.84561</v>
       </c>
       <c r="K73" t="n">
-        <v>558.84561</v>
+        <v>21.75723</v>
       </c>
       <c r="L73" t="n">
-        <v>21.75723</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
         <v>11.879</v>
       </c>
-      <c r="P73" t="n">
+      <c r="O73" t="n">
         <v>1492.70068</v>
       </c>
     </row>
@@ -11407,22 +11418,22 @@
       <c r="H74" t="n">
         <v>355.31565</v>
       </c>
+      <c r="I74" t="n">
+        <v>-0.08033999999999999</v>
+      </c>
       <c r="J74" t="n">
-        <v>-0.08033999999999999</v>
+        <v>671.73121</v>
       </c>
       <c r="K74" t="n">
-        <v>671.73121</v>
+        <v>24.50426</v>
       </c>
       <c r="L74" t="n">
-        <v>24.50426</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
         <v>11.582</v>
       </c>
-      <c r="P74" t="n">
+      <c r="O74" t="n">
         <v>1413.58084</v>
       </c>
     </row>
@@ -11453,22 +11464,22 @@
       <c r="H75" t="n">
         <v>377.52265</v>
       </c>
+      <c r="I75" t="n">
+        <v>-0.25647</v>
+      </c>
       <c r="J75" t="n">
-        <v>-0.25647</v>
+        <v>609.20379</v>
       </c>
       <c r="K75" t="n">
-        <v>609.20379</v>
+        <v>24.31483</v>
       </c>
       <c r="L75" t="n">
-        <v>24.31483</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
         <v>12.736</v>
       </c>
-      <c r="P75" t="n">
+      <c r="O75" t="n">
         <v>1291.81379</v>
       </c>
     </row>
@@ -11499,22 +11510,22 @@
       <c r="H76" t="n">
         <v>546.11119</v>
       </c>
+      <c r="I76" t="n">
+        <v>-0.16249</v>
+      </c>
       <c r="J76" t="n">
-        <v>-0.16249</v>
+        <v>507.99129</v>
       </c>
       <c r="K76" t="n">
-        <v>507.99129</v>
+        <v>26.69479</v>
       </c>
       <c r="L76" t="n">
-        <v>26.69479</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
         <v>18.391</v>
       </c>
-      <c r="P76" t="n">
+      <c r="O76" t="n">
         <v>1463.20158</v>
       </c>
     </row>
@@ -11545,22 +11556,22 @@
       <c r="H77" t="n">
         <v>430.36832</v>
       </c>
+      <c r="I77" t="n">
+        <v>-0.21213</v>
+      </c>
       <c r="J77" t="n">
-        <v>-0.21213</v>
+        <v>469.15559</v>
       </c>
       <c r="K77" t="n">
-        <v>469.15559</v>
+        <v>24.7889</v>
       </c>
       <c r="L77" t="n">
-        <v>24.7889</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
         <v>17.603</v>
       </c>
-      <c r="P77" t="n">
+      <c r="O77" t="n">
         <v>1353.51859</v>
       </c>
     </row>
@@ -11591,22 +11602,22 @@
       <c r="H78" t="n">
         <v>482.12101</v>
       </c>
+      <c r="I78" t="n">
+        <v>-0.15804</v>
+      </c>
       <c r="J78" t="n">
-        <v>-0.15804</v>
+        <v>601.96797</v>
       </c>
       <c r="K78" t="n">
-        <v>601.96797</v>
+        <v>25.43742</v>
       </c>
       <c r="L78" t="n">
-        <v>25.43742</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
         <v>17.465</v>
       </c>
-      <c r="P78" t="n">
+      <c r="O78" t="n">
         <v>1612.39718</v>
       </c>
     </row>
@@ -11637,22 +11648,22 @@
       <c r="H79" t="n">
         <v>560.46081</v>
       </c>
+      <c r="I79" t="n">
+        <v>-0.08892</v>
+      </c>
       <c r="J79" t="n">
-        <v>-0.08892</v>
+        <v>654.55828</v>
       </c>
       <c r="K79" t="n">
-        <v>654.55828</v>
+        <v>25.54181</v>
       </c>
       <c r="L79" t="n">
-        <v>25.54181</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
         <v>17.205</v>
       </c>
-      <c r="P79" t="n">
+      <c r="O79" t="n">
         <v>1683.60758</v>
       </c>
     </row>
@@ -11683,22 +11694,22 @@
       <c r="H80" t="n">
         <v>603.25443</v>
       </c>
+      <c r="I80" t="n">
+        <v>-0.15601</v>
+      </c>
       <c r="J80" t="n">
-        <v>-0.15601</v>
+        <v>671.90719</v>
       </c>
       <c r="K80" t="n">
-        <v>671.90719</v>
+        <v>22.83567</v>
       </c>
       <c r="L80" t="n">
-        <v>22.83567</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
         <v>19.365</v>
       </c>
-      <c r="P80" t="n">
+      <c r="O80" t="n">
         <v>1626.64303</v>
       </c>
     </row>
@@ -11729,22 +11740,22 @@
       <c r="H81" t="n">
         <v>648.43242</v>
       </c>
+      <c r="I81" t="n">
+        <v>-0.17407</v>
+      </c>
       <c r="J81" t="n">
-        <v>-0.17407</v>
+        <v>643.74085</v>
       </c>
       <c r="K81" t="n">
-        <v>643.74085</v>
+        <v>24.11321</v>
       </c>
       <c r="L81" t="n">
-        <v>24.11321</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
         <v>13.615</v>
       </c>
-      <c r="P81" t="n">
+      <c r="O81" t="n">
         <v>1696.22627</v>
       </c>
     </row>
@@ -11775,22 +11786,22 @@
       <c r="H82" t="n">
         <v>455.97318</v>
       </c>
+      <c r="I82" t="n">
+        <v>-0.35114</v>
+      </c>
       <c r="J82" t="n">
-        <v>-0.35114</v>
+        <v>418.03502</v>
       </c>
       <c r="K82" t="n">
-        <v>418.03502</v>
+        <v>16.71246</v>
       </c>
       <c r="L82" t="n">
-        <v>16.71246</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
         <v>4.762</v>
       </c>
-      <c r="P82" t="n">
+      <c r="O82" t="n">
         <v>1269.31792</v>
       </c>
     </row>
@@ -11821,22 +11832,22 @@
       <c r="H83" t="n">
         <v>447.91618</v>
       </c>
+      <c r="I83" t="n">
+        <v>-0.1347</v>
+      </c>
       <c r="J83" t="n">
-        <v>-0.1347</v>
+        <v>504.6305</v>
       </c>
       <c r="K83" t="n">
-        <v>504.6305</v>
+        <v>20.98221</v>
       </c>
       <c r="L83" t="n">
-        <v>20.98221</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
         <v>7.27</v>
       </c>
-      <c r="P83" t="n">
+      <c r="O83" t="n">
         <v>1539.34196</v>
       </c>
     </row>
@@ -11867,22 +11878,22 @@
       <c r="H84" t="n">
         <v>506.07769</v>
       </c>
+      <c r="I84" t="n">
+        <v>-0.17046</v>
+      </c>
       <c r="J84" t="n">
-        <v>-0.17046</v>
+        <v>544.04283</v>
       </c>
       <c r="K84" t="n">
-        <v>544.04283</v>
+        <v>20.06314</v>
       </c>
       <c r="L84" t="n">
-        <v>20.06314</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
         <v>7.147</v>
       </c>
-      <c r="P84" t="n">
+      <c r="O84" t="n">
         <v>1449.94349</v>
       </c>
     </row>
@@ -11913,22 +11924,22 @@
       <c r="H85" t="n">
         <v>368.70249</v>
       </c>
+      <c r="I85" t="n">
+        <v>-0.13526</v>
+      </c>
       <c r="J85" t="n">
-        <v>-0.13526</v>
+        <v>664.1544699999999</v>
       </c>
       <c r="K85" t="n">
-        <v>664.1544699999999</v>
+        <v>21.67834</v>
       </c>
       <c r="L85" t="n">
-        <v>21.67834</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
         <v>7.868</v>
       </c>
-      <c r="P85" t="n">
+      <c r="O85" t="n">
         <v>1406.15114</v>
       </c>
     </row>
@@ -11959,22 +11970,22 @@
       <c r="H86" t="n">
         <v>499.70874</v>
       </c>
+      <c r="I86" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
       <c r="J86" t="n">
-        <v>-0.07199999999999999</v>
+        <v>480.01905</v>
       </c>
       <c r="K86" t="n">
-        <v>480.01905</v>
+        <v>20.36761</v>
       </c>
       <c r="L86" t="n">
-        <v>20.36761</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
         <v>10.713</v>
       </c>
-      <c r="P86" t="n">
+      <c r="O86" t="n">
         <v>1343.90554</v>
       </c>
     </row>
@@ -12005,22 +12016,22 @@
       <c r="H87" t="n">
         <v>605.27151</v>
       </c>
+      <c r="I87" t="n">
+        <v>-0.056</v>
+      </c>
       <c r="J87" t="n">
-        <v>-0.056</v>
+        <v>371.18318</v>
       </c>
       <c r="K87" t="n">
-        <v>371.18318</v>
+        <v>20.76868</v>
       </c>
       <c r="L87" t="n">
-        <v>20.76868</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
         <v>12.02</v>
       </c>
-      <c r="P87" t="n">
+      <c r="O87" t="n">
         <v>1222.88659</v>
       </c>
     </row>
@@ -12051,22 +12062,22 @@
       <c r="H88" t="n">
         <v>568.2147200000001</v>
       </c>
+      <c r="I88" t="n">
+        <v>-0.066</v>
+      </c>
       <c r="J88" t="n">
-        <v>-0.066</v>
+        <v>500.60047</v>
       </c>
       <c r="K88" t="n">
-        <v>500.60047</v>
+        <v>22.7404</v>
       </c>
       <c r="L88" t="n">
-        <v>22.7404</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
         <v>10.343</v>
       </c>
-      <c r="P88" t="n">
+      <c r="O88" t="n">
         <v>1384.38761</v>
       </c>
     </row>
@@ -12097,22 +12108,22 @@
       <c r="H89" t="n">
         <v>610.9890799999999</v>
       </c>
+      <c r="I89" t="n">
+        <v>-0.289</v>
+      </c>
       <c r="J89" t="n">
-        <v>-0.289</v>
+        <v>438.96922</v>
       </c>
       <c r="K89" t="n">
-        <v>438.96922</v>
+        <v>24.41945</v>
       </c>
       <c r="L89" t="n">
-        <v>24.41945</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
         <v>9.563000000000001</v>
       </c>
-      <c r="P89" t="n">
+      <c r="O89" t="n">
         <v>1360.65282</v>
       </c>
     </row>
@@ -12143,22 +12154,22 @@
       <c r="H90" t="n">
         <v>609.03576</v>
       </c>
+      <c r="I90" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
       <c r="J90" t="n">
-        <v>-0.08500000000000001</v>
+        <v>500.27056</v>
       </c>
       <c r="K90" t="n">
-        <v>500.27056</v>
+        <v>23.92266</v>
       </c>
       <c r="L90" t="n">
-        <v>23.92266</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
         <v>8.303000000000001</v>
       </c>
-      <c r="P90" t="n">
+      <c r="O90" t="n">
         <v>1639.93235</v>
       </c>
     </row>
@@ -12189,22 +12200,22 @@
       <c r="H91" t="n">
         <v>687.0913</v>
       </c>
+      <c r="I91" t="n">
+        <v>-0.083</v>
+      </c>
       <c r="J91" t="n">
-        <v>-0.083</v>
+        <v>490.18036</v>
       </c>
       <c r="K91" t="n">
-        <v>490.18036</v>
+        <v>23.44574</v>
       </c>
       <c r="L91" t="n">
-        <v>23.44574</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
         <v>8.329000000000001</v>
       </c>
-      <c r="P91" t="n">
+      <c r="O91" t="n">
         <v>1668.81179</v>
       </c>
     </row>
@@ -12235,22 +12246,22 @@
       <c r="H92" t="n">
         <v>705.49623</v>
       </c>
+      <c r="I92" t="n">
+        <v>-0.171</v>
+      </c>
       <c r="J92" t="n">
-        <v>-0.171</v>
+        <v>412.06106</v>
       </c>
       <c r="K92" t="n">
-        <v>412.06106</v>
+        <v>23.67444</v>
       </c>
       <c r="L92" t="n">
-        <v>23.67444</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
         <v>14.818</v>
       </c>
-      <c r="P92" t="n">
+      <c r="O92" t="n">
         <v>1626.35647</v>
       </c>
     </row>
@@ -12281,22 +12292,22 @@
       <c r="H93" t="n">
         <v>741.3838</v>
       </c>
+      <c r="I93" t="n">
+        <v>-0.108</v>
+      </c>
       <c r="J93" t="n">
-        <v>-0.108</v>
+        <v>370.25862</v>
       </c>
       <c r="K93" t="n">
-        <v>370.25862</v>
+        <v>21.96905</v>
       </c>
       <c r="L93" t="n">
-        <v>21.96905</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
         <v>10.678</v>
       </c>
-      <c r="P93" t="n">
+      <c r="O93" t="n">
         <v>1685.84503</v>
       </c>
     </row>
@@ -12327,22 +12338,22 @@
       <c r="H94" t="n">
         <v>741.06868</v>
       </c>
+      <c r="I94" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="J94" t="n">
-        <v>-0.04</v>
+        <v>314.29002</v>
       </c>
       <c r="K94" t="n">
-        <v>314.29002</v>
+        <v>22.63688</v>
       </c>
       <c r="L94" t="n">
-        <v>22.63688</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
         <v>4.581</v>
       </c>
-      <c r="P94" t="n">
+      <c r="O94" t="n">
         <v>1592.15373</v>
       </c>
     </row>
@@ -12373,25 +12384,25 @@
       <c r="H95" t="n">
         <v>606.13444</v>
       </c>
+      <c r="I95" t="n">
+        <v>-0.236</v>
+      </c>
       <c r="J95" t="n">
-        <v>-0.236</v>
+        <v>371.79422</v>
       </c>
       <c r="K95" t="n">
-        <v>371.79422</v>
+        <v>19.66203</v>
       </c>
       <c r="L95" t="n">
-        <v>19.66203</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.487</v>
       </c>
       <c r="N95" t="n">
-        <v>3.487</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
         <v>1457.68081</v>
       </c>
     </row>
@@ -12422,25 +12433,25 @@
       <c r="H96" t="n">
         <v>617.44465</v>
       </c>
+      <c r="I96" t="n">
+        <v>-0.132</v>
+      </c>
       <c r="J96" t="n">
-        <v>-0.132</v>
+        <v>248.58447</v>
       </c>
       <c r="K96" t="n">
-        <v>248.58447</v>
+        <v>17.65832</v>
       </c>
       <c r="L96" t="n">
-        <v>17.65832</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.554</v>
       </c>
       <c r="N96" t="n">
-        <v>4.554</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
         <v>1251.50369</v>
       </c>
     </row>
@@ -12471,25 +12482,25 @@
       <c r="H97" t="n">
         <v>631.55182</v>
       </c>
+      <c r="I97" t="n">
+        <v>-0.038</v>
+      </c>
       <c r="J97" t="n">
-        <v>-0.038</v>
+        <v>333.73515</v>
       </c>
       <c r="K97" t="n">
-        <v>333.73515</v>
+        <v>18.53764</v>
       </c>
       <c r="L97" t="n">
-        <v>18.53764</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>8.539</v>
       </c>
       <c r="N97" t="n">
-        <v>8.539</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
         <v>1268.34671</v>
       </c>
     </row>
@@ -12520,25 +12531,25 @@
       <c r="H98" t="n">
         <v>581.38379</v>
       </c>
+      <c r="I98" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="J98" t="n">
-        <v>-0.13</v>
+        <v>177.9207</v>
       </c>
       <c r="K98" t="n">
-        <v>177.9207</v>
+        <v>20.8897</v>
       </c>
       <c r="L98" t="n">
-        <v>20.8897</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>12.439</v>
       </c>
       <c r="N98" t="n">
-        <v>12.439</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
         <v>1162.61452</v>
       </c>
     </row>
@@ -12569,25 +12580,25 @@
       <c r="H99" t="n">
         <v>482.04631</v>
       </c>
+      <c r="I99" t="n">
+        <v>-0.135</v>
+      </c>
       <c r="J99" t="n">
-        <v>-0.135</v>
+        <v>238.10255</v>
       </c>
       <c r="K99" t="n">
-        <v>238.10255</v>
+        <v>18.721</v>
       </c>
       <c r="L99" t="n">
-        <v>18.721</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>6.683</v>
       </c>
       <c r="N99" t="n">
-        <v>6.683</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
         <v>1063.7324</v>
       </c>
     </row>
@@ -12618,25 +12629,25 @@
       <c r="H100" t="n">
         <v>591.60947</v>
       </c>
+      <c r="I100" t="n">
+        <v>-0.631</v>
+      </c>
       <c r="J100" t="n">
-        <v>-0.631</v>
+        <v>185.64705</v>
       </c>
       <c r="K100" t="n">
-        <v>185.64705</v>
+        <v>23.984</v>
       </c>
       <c r="L100" t="n">
-        <v>23.984</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>13.867</v>
       </c>
       <c r="N100" t="n">
-        <v>13.867</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
         <v>1238.22517</v>
       </c>
     </row>
@@ -12667,25 +12678,25 @@
       <c r="H101" t="n">
         <v>590.47707</v>
       </c>
+      <c r="I101" t="n">
+        <v>-0.381</v>
+      </c>
       <c r="J101" t="n">
-        <v>-0.381</v>
+        <v>199.20697</v>
       </c>
       <c r="K101" t="n">
-        <v>199.20697</v>
+        <v>22.235</v>
       </c>
       <c r="L101" t="n">
-        <v>22.235</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>13.622</v>
       </c>
       <c r="N101" t="n">
-        <v>13.622</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
         <v>1263.61672</v>
       </c>
     </row>
@@ -12716,25 +12727,25 @@
       <c r="H102" t="n">
         <v>487.53716</v>
       </c>
+      <c r="I102" t="n">
+        <v>-0.364</v>
+      </c>
       <c r="J102" t="n">
-        <v>-0.364</v>
+        <v>520.5208</v>
       </c>
       <c r="K102" t="n">
-        <v>520.5208</v>
+        <v>22.686</v>
       </c>
       <c r="L102" t="n">
-        <v>22.686</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>11.12</v>
       </c>
       <c r="N102" t="n">
-        <v>11.12</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
         <v>1441.15383</v>
       </c>
     </row>
@@ -12765,25 +12776,25 @@
       <c r="H103" t="n">
         <v>582.19136</v>
       </c>
+      <c r="I103" t="n">
+        <v>-0.453</v>
+      </c>
       <c r="J103" t="n">
-        <v>-0.453</v>
+        <v>562.31229</v>
       </c>
       <c r="K103" t="n">
-        <v>562.31229</v>
+        <v>20.7913</v>
       </c>
       <c r="L103" t="n">
-        <v>20.7913</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>15.326</v>
       </c>
       <c r="N103" t="n">
-        <v>15.326</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
         <v>1503.58978</v>
       </c>
     </row>
@@ -12814,25 +12825,25 @@
       <c r="H104" t="n">
         <v>540.90515</v>
       </c>
+      <c r="I104" t="n">
+        <v>-0.386</v>
+      </c>
       <c r="J104" t="n">
-        <v>-0.386</v>
+        <v>571.26037</v>
       </c>
       <c r="K104" t="n">
-        <v>571.26037</v>
+        <v>21.586</v>
       </c>
       <c r="L104" t="n">
-        <v>21.586</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>22.954</v>
       </c>
       <c r="N104" t="n">
-        <v>22.954</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
         <v>1578.2994</v>
       </c>
     </row>
@@ -12863,25 +12874,25 @@
       <c r="H105" t="n">
         <v>437.20362</v>
       </c>
+      <c r="I105" t="n">
+        <v>-0.353</v>
+      </c>
       <c r="J105" t="n">
-        <v>-0.353</v>
+        <v>484.47333</v>
       </c>
       <c r="K105" t="n">
-        <v>484.47333</v>
+        <v>23.167</v>
       </c>
       <c r="L105" t="n">
-        <v>23.167</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>17.443</v>
       </c>
       <c r="N105" t="n">
-        <v>17.443</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
         <v>1507.63199</v>
       </c>
     </row>
@@ -12912,25 +12923,25 @@
       <c r="H106" t="n">
         <v>499.51351</v>
       </c>
+      <c r="I106" t="n">
+        <v>-0.304</v>
+      </c>
       <c r="J106" t="n">
-        <v>-0.304</v>
+        <v>491.86025</v>
       </c>
       <c r="K106" t="n">
-        <v>491.86025</v>
+        <v>21.426</v>
       </c>
       <c r="L106" t="n">
-        <v>21.426</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>11.131</v>
       </c>
       <c r="N106" t="n">
-        <v>11.131</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
         <v>1481.28907</v>
       </c>
     </row>
@@ -12961,25 +12972,25 @@
       <c r="H107" t="n">
         <v>605.94793</v>
       </c>
+      <c r="I107" t="n">
+        <v>-0.255</v>
+      </c>
       <c r="J107" t="n">
-        <v>-0.255</v>
+        <v>369.1408</v>
       </c>
       <c r="K107" t="n">
-        <v>369.1408</v>
+        <v>19.849</v>
       </c>
       <c r="L107" t="n">
-        <v>19.849</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5.702</v>
       </c>
       <c r="N107" t="n">
-        <v>5.702</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
         <v>1521.9599</v>
       </c>
     </row>
@@ -13010,25 +13021,25 @@
       <c r="H108" t="n">
         <v>661.45343</v>
       </c>
+      <c r="I108" t="n">
+        <v>-0.205</v>
+      </c>
       <c r="J108" t="n">
-        <v>-0.205</v>
+        <v>285.34501</v>
       </c>
       <c r="K108" t="n">
-        <v>285.34501</v>
+        <v>16.944</v>
       </c>
       <c r="L108" t="n">
-        <v>16.944</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>6.839</v>
       </c>
       <c r="N108" t="n">
-        <v>6.839</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
         <v>1316.89761</v>
       </c>
     </row>
@@ -13059,25 +13070,25 @@
       <c r="H109" t="n">
         <v>576.12352</v>
       </c>
+      <c r="I109" t="n">
+        <v>-0.248</v>
+      </c>
       <c r="J109" t="n">
-        <v>-0.248</v>
+        <v>181.87053</v>
       </c>
       <c r="K109" t="n">
-        <v>181.87053</v>
+        <v>18.125</v>
       </c>
       <c r="L109" t="n">
-        <v>18.125</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="N109" t="n">
-        <v>10.38</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
         <v>1271.5529</v>
       </c>
     </row>
@@ -13094,10 +13105,10 @@
         <v>190.836</v>
       </c>
       <c r="D110" t="n">
-        <v>140.67052</v>
+        <v>150.10063</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -13106,28 +13117,28 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>555.35429</v>
+        <v>573.60488</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-0.358</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.344</v>
+        <v>277.91419</v>
       </c>
       <c r="K110" t="n">
-        <v>277.91419</v>
+        <v>20.20984</v>
       </c>
       <c r="L110" t="n">
-        <v>14.39184</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>15.022</v>
       </c>
       <c r="N110" t="n">
-        <v>15.002</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1193.82484</v>
+        <v>1228.97954</v>
       </c>
     </row>
     <row r="111">
@@ -13143,10 +13154,10 @@
         <v>188.689</v>
       </c>
       <c r="D111" t="n">
-        <v>126.41158</v>
+        <v>136.41805</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>2.232</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -13155,28 +13166,28 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>444.8452</v>
+        <v>459.48407</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-0.419</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.406</v>
+        <v>327.82622</v>
       </c>
       <c r="K111" t="n">
-        <v>327.82622</v>
+        <v>20.39868</v>
       </c>
       <c r="L111" t="n">
-        <v>15.05972</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>21.673</v>
       </c>
       <c r="N111" t="n">
-        <v>21.649</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1124.07472</v>
+        <v>1156.30202</v>
       </c>
     </row>
     <row r="112">
@@ -13192,10 +13203,10 @@
         <v>330.265</v>
       </c>
       <c r="D112" t="n">
-        <v>221.425</v>
+        <v>231.89923</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>5.403</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -13204,28 +13215,28 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>452.66214</v>
+        <v>467.58732</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-0.8</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.789</v>
+        <v>186.43787</v>
       </c>
       <c r="K112" t="n">
-        <v>186.43787</v>
+        <v>24.63747</v>
       </c>
       <c r="L112" t="n">
-        <v>17.87947</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>13.464</v>
       </c>
       <c r="N112" t="n">
-        <v>13.448</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>1221.32848</v>
+        <v>1258.89389</v>
       </c>
     </row>
     <row r="113">
@@ -13241,10 +13252,10 @@
         <v>241.303</v>
       </c>
       <c r="D113" t="n">
-        <v>239.96965</v>
+        <v>250.2303</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>4.419</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -13253,28 +13264,28 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>458.6353</v>
+        <v>473.75395</v>
+      </c>
+      <c r="I113" t="n">
+        <v>-0.474</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.466</v>
+        <v>161.50405</v>
       </c>
       <c r="K113" t="n">
-        <v>161.50405</v>
+        <v>23.53074</v>
       </c>
       <c r="L113" t="n">
-        <v>17.15374</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>15.707</v>
       </c>
       <c r="N113" t="n">
-        <v>15.685</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>1133.78474</v>
+        <v>1169.97404</v>
       </c>
     </row>
     <row r="114">
@@ -13290,10 +13301,10 @@
         <v>307.555</v>
       </c>
       <c r="D114" t="n">
-        <v>100.79238</v>
+        <v>111.14575</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>6.515</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -13302,28 +13313,28 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>603.44453</v>
+        <v>623.24086</v>
+      </c>
+      <c r="I114" t="n">
+        <v>-0.48</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.47</v>
+        <v>296.2841</v>
       </c>
       <c r="K114" t="n">
-        <v>296.2841</v>
+        <v>24.42572</v>
       </c>
       <c r="L114" t="n">
-        <v>17.9132</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>17.359</v>
       </c>
       <c r="N114" t="n">
-        <v>17.358</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
-        <v>1342.87721</v>
+        <v>1386.04543</v>
       </c>
     </row>
     <row r="115">
@@ -13339,10 +13350,10 @@
         <v>283.861</v>
       </c>
       <c r="D115" t="n">
-        <v>150.89101</v>
+        <v>163.87058</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>3.137</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -13351,28 +13362,28 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>534.44904</v>
+        <v>551.88886</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>-0.281</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.269</v>
+        <v>387.41096</v>
       </c>
       <c r="K115" t="n">
-        <v>387.41096</v>
+        <v>24.24218</v>
       </c>
       <c r="L115" t="n">
-        <v>17.55318</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>26.713</v>
       </c>
       <c r="N115" t="n">
-        <v>26.713</v>
-      </c>
-      <c r="P115" t="n">
-        <v>1400.60919</v>
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1440.84258</v>
       </c>
     </row>
     <row r="116">
@@ -13388,10 +13399,10 @@
         <v>265.21</v>
       </c>
       <c r="D116" t="n">
-        <v>168.35061</v>
+        <v>179.71339</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -13400,28 +13411,28 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>614.50681</v>
+        <v>634.6822</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-0.125</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.114</v>
+        <v>405.67958</v>
       </c>
       <c r="K116" t="n">
-        <v>405.67958</v>
+        <v>25.58666</v>
       </c>
       <c r="L116" t="n">
-        <v>18.72066</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>23.948</v>
       </c>
       <c r="N116" t="n">
-        <v>23.938</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1496.29166</v>
+        <v>1537.59483</v>
       </c>
     </row>
     <row r="117">
@@ -13437,10 +13448,10 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>126.84726</v>
+        <v>134.42556</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>6.407</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -13449,28 +13460,28 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>785.86313</v>
+        <v>811.67228</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-0.043</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.035</v>
+        <v>301.62061</v>
       </c>
       <c r="K117" t="n">
-        <v>301.62061</v>
+        <v>25.24134</v>
       </c>
       <c r="L117" t="n">
-        <v>18.43434</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>16.814</v>
       </c>
       <c r="N117" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>1249.54034</v>
+        <v>1296.13779</v>
       </c>
     </row>
     <row r="118">
@@ -13486,10 +13497,10 @@
         <v>283.614</v>
       </c>
       <c r="D118" t="n">
-        <v>95.17400000000001</v>
+        <v>100.98385</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>4.747</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -13498,28 +13509,28 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>782.23017</v>
+        <v>807.82938</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-0.066</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.058</v>
+        <v>296.44984</v>
       </c>
       <c r="K118" t="n">
-        <v>296.44984</v>
+        <v>21.959</v>
       </c>
       <c r="L118" t="n">
-        <v>15.691</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>9.211</v>
       </c>
       <c r="N118" t="n">
-        <v>9.208</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>1482.30901</v>
+        <v>1524.72807</v>
       </c>
     </row>
     <row r="119">
@@ -13535,10 +13546,10 @@
         <v>150.908</v>
       </c>
       <c r="D119" t="n">
-        <v>202.62521</v>
+        <v>218.35744</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>4.696</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -13547,28 +13558,28 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>679.61851</v>
+        <v>699.55007</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-0.06</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.051</v>
+        <v>461.41729</v>
       </c>
       <c r="K119" t="n">
-        <v>461.41729</v>
+        <v>20.788</v>
       </c>
       <c r="L119" t="n">
-        <v>15.019</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="N119" t="n">
-        <v>7.997</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>1517.53401</v>
+        <v>1563.6648</v>
       </c>
     </row>
     <row r="120">
@@ -13584,10 +13595,10 @@
         <v>262.924</v>
       </c>
       <c r="D120" t="n">
-        <v>131.18392</v>
+        <v>140.42402</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>3.003</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -13596,28 +13607,28 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>602.7464</v>
+        <v>622.55695</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-0.055</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.047</v>
+        <v>379.32268</v>
       </c>
       <c r="K120" t="n">
-        <v>379.32268</v>
+        <v>20.8601</v>
       </c>
       <c r="L120" t="n">
-        <v>15.8261</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>11.475</v>
       </c>
       <c r="N120" t="n">
-        <v>11.466</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>1403.4221</v>
+        <v>1440.51075</v>
       </c>
     </row>
     <row r="121">
@@ -13633,10 +13644,10 @@
         <v>273.948</v>
       </c>
       <c r="D121" t="n">
-        <v>69.90688</v>
+        <v>81.78502</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1.871</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -13645,28 +13656,28 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>486.04527</v>
+        <v>501.97811</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-0.063</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.055</v>
+        <v>471.07686</v>
       </c>
       <c r="K121" t="n">
-        <v>471.07686</v>
+        <v>21.497</v>
       </c>
       <c r="L121" t="n">
-        <v>16.256</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>10.94</v>
       </c>
       <c r="N121" t="n">
-        <v>10.932</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>1328.11001</v>
+        <v>1363.03299</v>
       </c>
     </row>
     <row r="122">
@@ -13697,27 +13708,24 @@
         <v>567.9237000000001</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>-0.058</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.058</v>
+        <v>289.36482</v>
       </c>
       <c r="K122" t="n">
-        <v>289.36482</v>
+        <v>15.941</v>
       </c>
       <c r="L122" t="n">
-        <v>15.941</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>12.417</v>
       </c>
       <c r="N122" t="n">
-        <v>12.417</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
         <v>1241.536</v>
       </c>
     </row>
@@ -13734,7 +13742,7 @@
         <v>141.62</v>
       </c>
       <c r="D123" t="n">
-        <v>52.25907</v>
+        <v>52.25967</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -13746,28 +13754,28 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>556.0905299999999</v>
+        <v>556.08992</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-0.044</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.044</v>
+        <v>325.04641</v>
       </c>
       <c r="K123" t="n">
-        <v>325.04641</v>
+        <v>13.976</v>
       </c>
       <c r="L123" t="n">
-        <v>13.976</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>12.402</v>
       </c>
       <c r="N123" t="n">
-        <v>12.402</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1101.35001</v>
+        <v>1101.35</v>
       </c>
     </row>
     <row r="124">
@@ -13797,25 +13805,25 @@
       <c r="H124" t="n">
         <v>655.53219</v>
       </c>
+      <c r="I124" t="n">
+        <v>-0.059</v>
+      </c>
       <c r="J124" t="n">
-        <v>-0.059</v>
+        <v>227.32589</v>
       </c>
       <c r="K124" t="n">
-        <v>227.32589</v>
+        <v>17.912</v>
       </c>
       <c r="L124" t="n">
-        <v>17.912</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>21.248</v>
       </c>
       <c r="N124" t="n">
-        <v>21.248</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
         <v>1231.33</v>
       </c>
     </row>
@@ -13846,25 +13854,25 @@
       <c r="H125" t="n">
         <v>615.7113000000001</v>
       </c>
+      <c r="I125" t="n">
+        <v>-0.035</v>
+      </c>
       <c r="J125" t="n">
-        <v>-0.035</v>
+        <v>220.63338</v>
       </c>
       <c r="K125" t="n">
-        <v>220.63338</v>
+        <v>17.505</v>
       </c>
       <c r="L125" t="n">
-        <v>17.505</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>11.398</v>
       </c>
       <c r="N125" t="n">
-        <v>11.398</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
         <v>1260.588</v>
       </c>
     </row>
@@ -13895,25 +13903,25 @@
       <c r="H126" t="n">
         <v>643.92048</v>
       </c>
+      <c r="I126" t="n">
+        <v>-0.043</v>
+      </c>
       <c r="J126" t="n">
-        <v>-0.043</v>
+        <v>333.69196</v>
       </c>
       <c r="K126" t="n">
-        <v>333.69196</v>
+        <v>18.964</v>
       </c>
       <c r="L126" t="n">
-        <v>18.964</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>25.979</v>
       </c>
       <c r="N126" t="n">
-        <v>25.979</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
         <v>1426.335</v>
       </c>
     </row>
@@ -13944,25 +13952,25 @@
       <c r="H127" t="n">
         <v>739.11502</v>
       </c>
+      <c r="I127" t="n">
+        <v>-0.003</v>
+      </c>
       <c r="J127" t="n">
-        <v>-0.003</v>
+        <v>345.33208</v>
       </c>
       <c r="K127" t="n">
-        <v>345.33208</v>
+        <v>18.646</v>
       </c>
       <c r="L127" t="n">
-        <v>18.646</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>25.117</v>
       </c>
       <c r="N127" t="n">
-        <v>25.117</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
         <v>1492.03901</v>
       </c>
     </row>
@@ -13993,26 +14001,75 @@
       <c r="H128" t="n">
         <v>648.63659</v>
       </c>
+      <c r="I128" t="n">
+        <v>-0.136</v>
+      </c>
       <c r="J128" t="n">
-        <v>-0.136</v>
+        <v>413.97958</v>
       </c>
       <c r="K128" t="n">
-        <v>413.97958</v>
+        <v>18.66351</v>
       </c>
       <c r="L128" t="n">
-        <v>18.66351</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>29.736</v>
       </c>
       <c r="N128" t="n">
-        <v>29.736</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
         <v>1607.53651</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" t="n">
+        <v>267.339</v>
+      </c>
+      <c r="D129" t="n">
+        <v>169.83288</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>716.81976</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="J129" t="n">
+        <v>430.62336</v>
+      </c>
+      <c r="K129" t="n">
+        <v>17.82315</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>25.919</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1628.34515</v>
       </c>
     </row>
   </sheetData>
